--- a/model/Outputs/11. Interest rate/20/Output Files/0.2/Output_12_36.xlsx
+++ b/model/Outputs/11. Interest rate/20/Output Files/0.2/Output_12_36.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2212823.449348562</v>
+        <v>2213894.573060837</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14697842.82031929</v>
+        <v>14697842.82031947</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14697842.82031929</v>
+        <v>14697842.82031947</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>657188.6984938876</v>
+        <v>657188.6984940342</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>657188.6984938876</v>
+        <v>657188.6984940342</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>30280594.10822123</v>
+        <v>30280594.1082212</v>
       </c>
     </row>
   </sheetData>
@@ -733,19 +733,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>92.54517864405815</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -754,7 +754,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>209.5726123064429</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -790,10 +790,10 @@
         <v>4.473444462796863</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1959257979225981</v>
+        <v>353.4947099971142</v>
       </c>
       <c r="V3" t="n">
-        <v>374</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W3" t="n">
         <v>32.37314290982852</v>
@@ -909,10 +909,10 @@
         <v>3.34732203575993</v>
       </c>
       <c r="H5" t="n">
-        <v>3.81023156784903</v>
+        <v>5.608919435675552</v>
       </c>
       <c r="I5" t="n">
-        <v>1.79868786782652</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -976,10 +976,10 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>123.8166229101007</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -988,7 +988,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>128.9709564352694</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1033,10 +1033,10 @@
         <v>14.51066719152016</v>
       </c>
       <c r="W6" t="n">
-        <v>32.37314290982852</v>
+        <v>374</v>
       </c>
       <c r="X6" t="n">
-        <v>19.86273944538755</v>
+        <v>374</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1143,13 +1143,13 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>3.34732203575993</v>
+        <v>3.347322035759929</v>
       </c>
       <c r="H8" t="n">
-        <v>3.81023156784903</v>
+        <v>5.608919435675665</v>
       </c>
       <c r="I8" t="n">
-        <v>1.79868786782652</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1216,7 +1216,7 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>307.4698632043681</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1225,7 +1225,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>330.0491815260438</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1255,16 +1255,16 @@
         <v>145.073529241423</v>
       </c>
       <c r="R9" t="n">
-        <v>158.1721839527247</v>
+        <v>133.6519859716246</v>
       </c>
       <c r="S9" t="n">
-        <v>374</v>
+        <v>62.48881128536602</v>
       </c>
       <c r="T9" t="n">
-        <v>374</v>
+        <v>4.473444462796834</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1959257979225981</v>
+        <v>0.1959257979225968</v>
       </c>
       <c r="V9" t="n">
         <v>14.51066719152016</v>
@@ -1273,10 +1273,10 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X9" t="n">
-        <v>19.86273944538755</v>
+        <v>374</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10">
@@ -1322,10 +1322,10 @@
         <v>91.79905402550071</v>
       </c>
       <c r="N10" t="n">
-        <v>143.0380916651276</v>
+        <v>143.0380916651275</v>
       </c>
       <c r="O10" t="n">
-        <v>214.4472689970478</v>
+        <v>214.4472689970477</v>
       </c>
       <c r="P10" t="n">
         <v>265.2018645413922</v>
@@ -1374,16 +1374,16 @@
         <v>91.33915573984979</v>
       </c>
       <c r="E11" t="n">
-        <v>84.66720461037373</v>
+        <v>85.36328960686865</v>
       </c>
       <c r="F11" t="n">
         <v>85.88962870801186</v>
       </c>
       <c r="G11" t="n">
-        <v>83.28199540259411</v>
+        <v>83.28199540259408</v>
       </c>
       <c r="H11" t="n">
-        <v>73.89995518593948</v>
+        <v>73.89995518593946</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1431,7 +1431,7 @@
         <v>319.3734759809475</v>
       </c>
       <c r="X11" t="n">
-        <v>273.2818334606677</v>
+        <v>272.5857484641728</v>
       </c>
       <c r="Y11" t="n">
         <v>192.3174326828064</v>
@@ -1453,19 +1453,19 @@
         <v>28.93768689770263</v>
       </c>
       <c r="E12" t="n">
-        <v>23.67209722191262</v>
+        <v>56.66675767574525</v>
       </c>
       <c r="F12" t="n">
-        <v>20.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G12" t="n">
         <v>324.9501396486123</v>
       </c>
       <c r="H12" t="n">
-        <v>5.544181526043773</v>
+        <v>5.544181526043758</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>189.9476123064429</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1492,16 +1492,16 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>402.2042587319003</v>
+        <v>179.2619859716245</v>
       </c>
       <c r="S12" t="n">
         <v>132.901311285366</v>
       </c>
       <c r="T12" t="n">
-        <v>83.17594446279683</v>
+        <v>83.17594446279685</v>
       </c>
       <c r="U12" t="n">
-        <v>400.1584257979226</v>
+        <v>81.15842579792258</v>
       </c>
       <c r="V12" t="n">
         <v>95.51066719152016</v>
@@ -1510,10 +1510,10 @@
         <v>113.3731429098285</v>
       </c>
       <c r="X12" t="n">
-        <v>419.8627394453875</v>
+        <v>100.8627394453875</v>
       </c>
       <c r="Y12" t="n">
-        <v>80.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="13">
@@ -1553,13 +1553,13 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>6.155529797123435</v>
+        <v>3.305168319657098</v>
       </c>
       <c r="M13" t="n">
-        <v>97.89093927140236</v>
+        <v>97.89093927140237</v>
       </c>
       <c r="N13" t="n">
-        <v>148.0607629745462</v>
+        <v>150.9111244520127</v>
       </c>
       <c r="O13" t="n">
         <v>227.9026788331133</v>
@@ -1571,10 +1571,10 @@
         <v>351.422266425598</v>
       </c>
       <c r="R13" t="n">
-        <v>377.845046013938</v>
+        <v>377.8450460139379</v>
       </c>
       <c r="S13" t="n">
-        <v>31.84005347334724</v>
+        <v>31.84005347334727</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1617,10 +1617,10 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G14" t="n">
-        <v>83.28199540259411</v>
+        <v>83.28199540259408</v>
       </c>
       <c r="H14" t="n">
-        <v>73.89995518593948</v>
+        <v>73.89995518593946</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1687,19 +1687,19 @@
         <v>42.09991244551929</v>
       </c>
       <c r="D15" t="n">
-        <v>251.8799596579785</v>
+        <v>28.93768689770263</v>
       </c>
       <c r="E15" t="n">
-        <v>342.6720972219126</v>
+        <v>23.67209722191262</v>
       </c>
       <c r="F15" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G15" t="n">
-        <v>324.9501396486123</v>
+        <v>5.950139648612264</v>
       </c>
       <c r="H15" t="n">
-        <v>5.544181526043773</v>
+        <v>5.544181526043758</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1729,25 +1729,25 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>179.2619859716246</v>
+        <v>179.2619859716245</v>
       </c>
       <c r="S15" t="n">
         <v>132.901311285366</v>
       </c>
       <c r="T15" t="n">
-        <v>83.17594446279683</v>
+        <v>83.17594446279685</v>
       </c>
       <c r="U15" t="n">
-        <v>81.1584257979226</v>
+        <v>81.15842579792258</v>
       </c>
       <c r="V15" t="n">
-        <v>95.51066719152016</v>
+        <v>318.4529399517959</v>
       </c>
       <c r="W15" t="n">
-        <v>113.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X15" t="n">
-        <v>100.8627394453875</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y15" t="n">
         <v>80.39139276613435</v>
@@ -1790,16 +1790,16 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>6.155529797123435</v>
+        <v>6.155529797123449</v>
       </c>
       <c r="M16" t="n">
-        <v>97.89093927140236</v>
+        <v>97.89093927140237</v>
       </c>
       <c r="N16" t="n">
         <v>150.9111244520127</v>
       </c>
       <c r="O16" t="n">
-        <v>225.0523173556467</v>
+        <v>227.9026788331133</v>
       </c>
       <c r="P16" t="n">
         <v>288.4057989676218</v>
@@ -1808,10 +1808,10 @@
         <v>351.422266425598</v>
       </c>
       <c r="R16" t="n">
-        <v>377.845046013938</v>
+        <v>377.8450460139379</v>
       </c>
       <c r="S16" t="n">
-        <v>31.84005347334724</v>
+        <v>28.9896919958832</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1918,16 +1918,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>288.4988294066021</v>
+        <v>65.55655664632661</v>
       </c>
       <c r="C18" t="n">
-        <v>361.0999124455193</v>
+        <v>42.09991244551929</v>
       </c>
       <c r="D18" t="n">
-        <v>347.9376868977026</v>
+        <v>28.93768689770263</v>
       </c>
       <c r="E18" t="n">
-        <v>342.6720972219126</v>
+        <v>23.67209722191262</v>
       </c>
       <c r="F18" t="n">
         <v>20.63624233787687</v>
@@ -1978,16 +1978,16 @@
         <v>81.15842579792258</v>
       </c>
       <c r="V18" t="n">
-        <v>95.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W18" t="n">
-        <v>113.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X18" t="n">
-        <v>100.8627394453875</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y18" t="n">
-        <v>80.39139276613435</v>
+        <v>303.3336655264099</v>
       </c>
     </row>
     <row r="19">
@@ -2048,7 +2048,7 @@
         <v>377.8450460139379</v>
       </c>
       <c r="S19" t="n">
-        <v>28.98969199588095</v>
+        <v>28.9896919958832</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2079,7 +2079,7 @@
         <v>162.9993129555745</v>
       </c>
       <c r="C20" t="n">
-        <v>130.4745782429939</v>
+        <v>129.778493246499</v>
       </c>
       <c r="D20" t="n">
         <v>91.33915573984979</v>
@@ -2127,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>141.5319320520589</v>
+        <v>142.2280170485541</v>
       </c>
       <c r="T20" t="n">
         <v>261.2171194170061</v>
@@ -2155,19 +2155,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>384.5565566463266</v>
+        <v>288.4988294066021</v>
       </c>
       <c r="C21" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D21" t="n">
-        <v>251.8799596579781</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E21" t="n">
-        <v>342.6720972219126</v>
+        <v>23.67209722191262</v>
       </c>
       <c r="F21" t="n">
-        <v>20.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G21" t="n">
         <v>5.950139648612248</v>
@@ -2276,7 +2276,7 @@
         <v>227.9026788331133</v>
       </c>
       <c r="P22" t="n">
-        <v>285.5554374901554</v>
+        <v>288.4057989676218</v>
       </c>
       <c r="Q22" t="n">
         <v>351.422266425598</v>
@@ -2285,7 +2285,7 @@
         <v>377.845046013938</v>
       </c>
       <c r="S22" t="n">
-        <v>31.84005347334724</v>
+        <v>28.98969199588269</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2328,7 +2328,7 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G23" t="n">
-        <v>83.28199540259408</v>
+        <v>82.58591040609919</v>
       </c>
       <c r="H23" t="n">
         <v>73.89995518593946</v>
@@ -2364,7 +2364,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>141.5319320521385</v>
+        <v>142.2280170485541</v>
       </c>
       <c r="T23" t="n">
         <v>261.2171194170061</v>
@@ -2398,16 +2398,16 @@
         <v>42.09991244551929</v>
       </c>
       <c r="D24" t="n">
-        <v>347.9376868977026</v>
+        <v>28.93768689770263</v>
       </c>
       <c r="E24" t="n">
-        <v>342.6720972219126</v>
+        <v>23.67209722191262</v>
       </c>
       <c r="F24" t="n">
-        <v>339.6362423378769</v>
+        <v>171.2649858567294</v>
       </c>
       <c r="G24" t="n">
-        <v>5.950139648612264</v>
+        <v>324.9501396486123</v>
       </c>
       <c r="H24" t="n">
         <v>5.544181526043758</v>
@@ -2437,19 +2437,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>72.31352924142297</v>
       </c>
       <c r="R24" t="n">
-        <v>179.2619859716245</v>
+        <v>498.2619859716245</v>
       </c>
       <c r="S24" t="n">
-        <v>355.8435840456418</v>
+        <v>132.901311285366</v>
       </c>
       <c r="T24" t="n">
         <v>83.17594446279685</v>
       </c>
       <c r="U24" t="n">
-        <v>81.15842579792258</v>
+        <v>400.1584257979226</v>
       </c>
       <c r="V24" t="n">
         <v>95.51066719152016</v>
@@ -2504,7 +2504,7 @@
         <v>6.155529797123449</v>
       </c>
       <c r="M25" t="n">
-        <v>97.89093927140237</v>
+        <v>95.04057779393607</v>
       </c>
       <c r="N25" t="n">
         <v>150.9111244520127</v>
@@ -2522,7 +2522,7 @@
         <v>377.8450460139379</v>
       </c>
       <c r="S25" t="n">
-        <v>28.98969199588095</v>
+        <v>31.84005347334727</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2565,7 +2565,7 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G26" t="n">
-        <v>82.58591040625494</v>
+        <v>83.28199540259411</v>
       </c>
       <c r="H26" t="n">
         <v>73.89995518593948</v>
@@ -2616,7 +2616,7 @@
         <v>319.3734759809475</v>
       </c>
       <c r="X26" t="n">
-        <v>273.2818334606677</v>
+        <v>272.5857484642297</v>
       </c>
       <c r="Y26" t="n">
         <v>192.3174326828064</v>
@@ -2641,16 +2641,16 @@
         <v>23.67209722191262</v>
       </c>
       <c r="F27" t="n">
-        <v>339.6362423378769</v>
+        <v>20.63624233787687</v>
       </c>
       <c r="G27" t="n">
-        <v>5.950139648612248</v>
+        <v>324.9501396486123</v>
       </c>
       <c r="H27" t="n">
         <v>5.544181526043773</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>189.9476123064429</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2680,7 +2680,7 @@
         <v>498.2619859716245</v>
       </c>
       <c r="S27" t="n">
-        <v>451.901311285366</v>
+        <v>132.901311285366</v>
       </c>
       <c r="T27" t="n">
         <v>83.17594446279683</v>
@@ -2689,7 +2689,7 @@
         <v>81.1584257979226</v>
       </c>
       <c r="V27" t="n">
-        <v>246.1394107103725</v>
+        <v>375.1917984039295</v>
       </c>
       <c r="W27" t="n">
         <v>113.3731429098285</v>
@@ -2744,7 +2744,7 @@
         <v>97.89093927140236</v>
       </c>
       <c r="N28" t="n">
-        <v>150.9111244520127</v>
+        <v>148.0607629745466</v>
       </c>
       <c r="O28" t="n">
         <v>227.9026788331133</v>
@@ -2759,7 +2759,7 @@
         <v>377.845046013938</v>
       </c>
       <c r="S28" t="n">
-        <v>28.98969199588131</v>
+        <v>31.84005347334724</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2802,10 +2802,10 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G29" t="n">
-        <v>82.5859104061784</v>
+        <v>83.28199540259408</v>
       </c>
       <c r="H29" t="n">
-        <v>73.89995518593948</v>
+        <v>73.89995518593946</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2838,7 +2838,7 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>142.2280170485541</v>
+        <v>141.5319320520764</v>
       </c>
       <c r="T29" t="n">
         <v>261.2171194170061</v>
@@ -2872,16 +2872,16 @@
         <v>42.09991244551929</v>
       </c>
       <c r="D30" t="n">
-        <v>347.9376868977026</v>
+        <v>251.879959657978</v>
       </c>
       <c r="E30" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F30" t="n">
-        <v>20.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G30" t="n">
-        <v>5.950139648612248</v>
+        <v>5.950139648612264</v>
       </c>
       <c r="H30" t="n">
         <v>324.5441815260438</v>
@@ -2914,16 +2914,16 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>179.2619859716246</v>
+        <v>179.2619859716245</v>
       </c>
       <c r="S30" t="n">
         <v>132.901311285366</v>
       </c>
       <c r="T30" t="n">
-        <v>306.1182172230727</v>
+        <v>83.17594446279685</v>
       </c>
       <c r="U30" t="n">
-        <v>81.1584257979226</v>
+        <v>81.15842579792258</v>
       </c>
       <c r="V30" t="n">
         <v>95.51066719152016</v>
@@ -2975,10 +2975,10 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>3.305168319657323</v>
+        <v>6.155529797123449</v>
       </c>
       <c r="M31" t="n">
-        <v>97.89093927140236</v>
+        <v>97.89093927140237</v>
       </c>
       <c r="N31" t="n">
         <v>150.9111244520127</v>
@@ -2990,13 +2990,13 @@
         <v>288.4057989676218</v>
       </c>
       <c r="Q31" t="n">
-        <v>351.422266425598</v>
+        <v>348.5719049481314</v>
       </c>
       <c r="R31" t="n">
-        <v>377.845046013938</v>
+        <v>377.8450460139379</v>
       </c>
       <c r="S31" t="n">
-        <v>31.84005347334724</v>
+        <v>31.84005347334727</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3039,10 +3039,10 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G32" t="n">
-        <v>82.58591040625494</v>
+        <v>83.28199540259408</v>
       </c>
       <c r="H32" t="n">
-        <v>73.89995518593948</v>
+        <v>73.89995518593946</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3075,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>142.2280170485541</v>
+        <v>141.531932052116</v>
       </c>
       <c r="T32" t="n">
         <v>261.2171194170061</v>
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>384.5565566463266</v>
+        <v>65.55655664632661</v>
       </c>
       <c r="C33" t="n">
         <v>42.09991244551929</v>
@@ -3115,16 +3115,16 @@
         <v>23.67209722191262</v>
       </c>
       <c r="F33" t="n">
-        <v>339.6362423378769</v>
+        <v>20.63624233787687</v>
       </c>
       <c r="G33" t="n">
-        <v>5.950139648612248</v>
+        <v>324.9501396486123</v>
       </c>
       <c r="H33" t="n">
-        <v>38.5388419798764</v>
+        <v>156.1729250448959</v>
       </c>
       <c r="I33" t="n">
-        <v>189.9476123064429</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3148,28 +3148,28 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>72.31352924142297</v>
       </c>
       <c r="R33" t="n">
-        <v>179.2619859716246</v>
+        <v>179.2619859716245</v>
       </c>
       <c r="S33" t="n">
         <v>132.901311285366</v>
       </c>
       <c r="T33" t="n">
-        <v>83.17594446279683</v>
+        <v>83.17594446279685</v>
       </c>
       <c r="U33" t="n">
-        <v>81.1584257979226</v>
+        <v>81.15842579792258</v>
       </c>
       <c r="V33" t="n">
-        <v>95.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W33" t="n">
-        <v>113.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X33" t="n">
-        <v>419.8627394453875</v>
+        <v>100.8627394453875</v>
       </c>
       <c r="Y33" t="n">
         <v>80.39139276613435</v>
@@ -3212,10 +3212,10 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>6.155529797123435</v>
+        <v>6.155529797123449</v>
       </c>
       <c r="M34" t="n">
-        <v>97.89093927140236</v>
+        <v>97.89093927140237</v>
       </c>
       <c r="N34" t="n">
         <v>150.9111244520127</v>
@@ -3230,10 +3230,10 @@
         <v>351.422266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>377.845046013938</v>
+        <v>374.9946845364714</v>
       </c>
       <c r="S34" t="n">
-        <v>28.98969199589392</v>
+        <v>31.84005347334727</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>64.22801704855405</v>
+        <v>60.92708723805543</v>
       </c>
       <c r="T35" t="n">
         <v>183.2171194170061</v>
@@ -3327,7 +3327,7 @@
         <v>241.3734759809475</v>
       </c>
       <c r="X35" t="n">
-        <v>191.9809036502679</v>
+        <v>195.2818334606677</v>
       </c>
       <c r="Y35" t="n">
         <v>114.3174326828064</v>
@@ -3340,7 +3340,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>374.0000000000201</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -3349,7 +3349,7 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>189.9476123064429</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3385,31 +3385,31 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>72.31352924142297</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>101.2619859716246</v>
       </c>
       <c r="S36" t="n">
-        <v>54.90131128536602</v>
+        <v>164.3715131090992</v>
       </c>
       <c r="T36" t="n">
-        <v>5.175944462796835</v>
+        <v>374.0000000000201</v>
       </c>
       <c r="U36" t="n">
         <v>3.158425797922597</v>
       </c>
       <c r="V36" t="n">
-        <v>17.51066719152016</v>
+        <v>374.0000000000201</v>
       </c>
       <c r="W36" t="n">
         <v>35.37314290982852</v>
       </c>
       <c r="X36" t="n">
-        <v>255.1044836112602</v>
+        <v>22.86273944538755</v>
       </c>
       <c r="Y36" t="n">
-        <v>374.0000000000583</v>
+        <v>2.391392766134345</v>
       </c>
     </row>
     <row r="37">
@@ -3513,7 +3513,7 @@
         <v>7.889628708011855</v>
       </c>
       <c r="G38" t="n">
-        <v>5.281995402594077</v>
+        <v>5.2819954025941</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -3549,10 +3549,10 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>60.92708723815424</v>
+        <v>64.22801704855405</v>
       </c>
       <c r="T38" t="n">
-        <v>183.2171194170061</v>
+        <v>179.9161896065074</v>
       </c>
       <c r="U38" t="n">
         <v>252.1032663978569</v>
@@ -3583,7 +3583,7 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -3592,10 +3592,10 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>253.154211558318</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>324.5441815260438</v>
       </c>
       <c r="I39" t="n">
         <v>189.9476123064429</v>
@@ -3625,22 +3625,22 @@
         <v>72.31352924142297</v>
       </c>
       <c r="R39" t="n">
-        <v>361.219890605367</v>
+        <v>101.2619859716246</v>
       </c>
       <c r="S39" t="n">
-        <v>54.90131128536603</v>
+        <v>54.90131128536602</v>
       </c>
       <c r="T39" t="n">
-        <v>5.175944462796849</v>
+        <v>374.0000000000455</v>
       </c>
       <c r="U39" t="n">
-        <v>3.158425797922575</v>
+        <v>3.158425797922597</v>
       </c>
       <c r="V39" t="n">
         <v>17.51066719152016</v>
       </c>
       <c r="W39" t="n">
-        <v>374.0000000000928</v>
+        <v>35.37314290982852</v>
       </c>
       <c r="X39" t="n">
         <v>22.86273944538755</v>
@@ -3689,10 +3689,10 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>19.89093927140237</v>
+        <v>19.89093927140236</v>
       </c>
       <c r="N40" t="n">
-        <v>72.9111244520127</v>
+        <v>72.91112445201273</v>
       </c>
       <c r="O40" t="n">
         <v>149.9026788331133</v>
@@ -3704,7 +3704,7 @@
         <v>273.422266425598</v>
       </c>
       <c r="R40" t="n">
-        <v>299.8450460139379</v>
+        <v>299.845046013938</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -3735,7 +3735,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>188.9993129555745</v>
       </c>
       <c r="C41" t="n">
         <v>156.4745782429939</v>
@@ -3747,7 +3747,7 @@
         <v>111.3632896068686</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>111.8896287080119</v>
       </c>
       <c r="G41" t="n">
         <v>109.2819954025941</v>
@@ -3786,25 +3786,25 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>168.2280170485541</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>287.2171194170061</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>56.24161337540206</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>345.3734759809475</v>
+        <v>337.8538514754181</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>218.3174326828064</v>
       </c>
     </row>
     <row r="42">
@@ -3832,7 +3832,7 @@
         <v>31.95013964861226</v>
       </c>
       <c r="H42" t="n">
-        <v>31.54418152604376</v>
+        <v>33.93095497152576</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3877,7 +3877,7 @@
         <v>121.5106671915202</v>
       </c>
       <c r="W42" t="n">
-        <v>141.7599163554093</v>
+        <v>139.3731429098285</v>
       </c>
       <c r="X42" t="n">
         <v>126.8627394453875</v>
@@ -3923,28 +3923,28 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>32.15552979712345</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>123.8909392714024</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>176.9111244520127</v>
       </c>
       <c r="O43" t="n">
-        <v>253.9026788331133</v>
+        <v>42.5980297946369</v>
       </c>
       <c r="P43" t="n">
         <v>314.4057989676218</v>
       </c>
       <c r="Q43" t="n">
-        <v>374.0000000001383</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>179.4929979558174</v>
+        <v>374.0000000005462</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>57.84005347334727</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3975,10 +3975,10 @@
         <v>188.9993129555745</v>
       </c>
       <c r="C44" t="n">
-        <v>156.4745782429939</v>
+        <v>37.68885750868425</v>
       </c>
       <c r="D44" t="n">
-        <v>117.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
         <v>111.3632896068686</v>
@@ -4023,16 +4023,16 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>168.2280170485541</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>287.2171194170061</v>
       </c>
       <c r="U44" t="n">
-        <v>356.1032663978569</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>336.8510241668239</v>
       </c>
       <c r="W44" t="n">
         <v>0</v>
@@ -4041,7 +4041,7 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>200.0680177604665</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -4069,7 +4069,7 @@
         <v>31.95013964861225</v>
       </c>
       <c r="H45" t="n">
-        <v>31.54418152604377</v>
+        <v>33.93095497152588</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4096,7 +4096,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.386773445580913</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>205.2619859716246</v>
@@ -4163,10 +4163,10 @@
         <v>32.15552979712344</v>
       </c>
       <c r="M46" t="n">
-        <v>123.8909392714024</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>176.9111244520127</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>253.9026788331133</v>
@@ -4175,13 +4175,13 @@
         <v>314.4057989676218</v>
       </c>
       <c r="Q46" t="n">
-        <v>220.5354044354171</v>
+        <v>89.49741468477497</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>374.0000000007099</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>57.84005347334724</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -4321,25 +4321,25 @@
         <v>29.92</v>
       </c>
       <c r="J2" t="n">
-        <v>400.18</v>
+        <v>29.92</v>
       </c>
       <c r="K2" t="n">
-        <v>770.4399999999999</v>
+        <v>81.5583303517588</v>
       </c>
       <c r="L2" t="n">
-        <v>834.5019149748742</v>
+        <v>145.6202453266332</v>
       </c>
       <c r="M2" t="n">
-        <v>1204.761914974874</v>
+        <v>515.8802453266331</v>
       </c>
       <c r="N2" t="n">
-        <v>1437.908108133742</v>
+        <v>697.388108133742</v>
       </c>
       <c r="O2" t="n">
-        <v>1437.908108133742</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="P2" t="n">
-        <v>1496</v>
+        <v>1125.74</v>
       </c>
       <c r="Q2" t="n">
         <v>1496</v>
@@ -4376,25 +4376,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>338.3034554400513</v>
+        <v>722.3343126211507</v>
       </c>
       <c r="C3" t="n">
-        <v>244.8234770117097</v>
+        <v>722.3343126211507</v>
       </c>
       <c r="D3" t="n">
-        <v>244.8234770117097</v>
+        <v>722.3343126211507</v>
       </c>
       <c r="E3" t="n">
-        <v>244.8234770117097</v>
+        <v>376.2008810838653</v>
       </c>
       <c r="F3" t="n">
-        <v>244.8234770117097</v>
+        <v>33.13396963146437</v>
       </c>
       <c r="G3" t="n">
-        <v>244.8234770117097</v>
+        <v>33.13396963146437</v>
       </c>
       <c r="H3" t="n">
-        <v>244.8234770117097</v>
+        <v>33.13396963146437</v>
       </c>
       <c r="I3" t="n">
         <v>33.13396963146437</v>
@@ -4433,19 +4433,19 @@
         <v>1146.820433372515</v>
       </c>
       <c r="U3" t="n">
-        <v>1146.622528526128</v>
+        <v>789.7550697390661</v>
       </c>
       <c r="V3" t="n">
-        <v>768.8447507483504</v>
+        <v>775.097830151672</v>
       </c>
       <c r="W3" t="n">
-        <v>736.1446063949883</v>
+        <v>742.3976857983099</v>
       </c>
       <c r="X3" t="n">
-        <v>716.0812332178291</v>
+        <v>722.3343126211507</v>
       </c>
       <c r="Y3" t="n">
-        <v>716.0812332178291</v>
+        <v>722.3343126211507</v>
       </c>
     </row>
     <row r="4">
@@ -4455,34 +4455,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1098.487249727908</v>
+        <v>711.1601720474662</v>
       </c>
       <c r="C4" t="n">
-        <v>1098.487249727908</v>
+        <v>837.162177865902</v>
       </c>
       <c r="D4" t="n">
-        <v>1098.487249727908</v>
+        <v>837.162177865902</v>
       </c>
       <c r="E4" t="n">
-        <v>1098.487249727908</v>
+        <v>837.162177865902</v>
       </c>
       <c r="F4" t="n">
-        <v>1098.487249727908</v>
+        <v>837.162177865902</v>
       </c>
       <c r="G4" t="n">
-        <v>1251.462556240126</v>
+        <v>990.7508388347544</v>
       </c>
       <c r="H4" t="n">
-        <v>1251.462556240126</v>
+        <v>990.7508388347544</v>
       </c>
       <c r="I4" t="n">
-        <v>1251.462556240126</v>
+        <v>1217.359813508542</v>
       </c>
       <c r="J4" t="n">
-        <v>1251.462556240126</v>
+        <v>1255.222976822941</v>
       </c>
       <c r="K4" t="n">
-        <v>1382.983127881912</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="L4" t="n">
         <v>1386.743548464727</v>
@@ -4509,22 +4509,22 @@
         <v>29.92</v>
       </c>
       <c r="T4" t="n">
-        <v>218.7737217817557</v>
+        <v>29.92</v>
       </c>
       <c r="U4" t="n">
-        <v>465.3348468790587</v>
+        <v>276.481125097303</v>
       </c>
       <c r="V4" t="n">
-        <v>664.1562397650047</v>
+        <v>276.481125097303</v>
       </c>
       <c r="W4" t="n">
-        <v>836.0471580246821</v>
+        <v>448.3720433569805</v>
       </c>
       <c r="X4" t="n">
-        <v>987.0779490488756</v>
+        <v>599.402834381174</v>
       </c>
       <c r="Y4" t="n">
-        <v>1098.487249727908</v>
+        <v>599.402834381174</v>
       </c>
     </row>
     <row r="5">
@@ -4552,7 +4552,7 @@
         <v>35.58557518755106</v>
       </c>
       <c r="H5" t="n">
-        <v>31.736856432148</v>
+        <v>29.92</v>
       </c>
       <c r="I5" t="n">
         <v>29.92</v>
@@ -4561,16 +4561,16 @@
         <v>400.18</v>
       </c>
       <c r="K5" t="n">
-        <v>770.4399999999999</v>
+        <v>451.8183303517587</v>
       </c>
       <c r="L5" t="n">
-        <v>1067.648108133742</v>
+        <v>515.8802453266331</v>
       </c>
       <c r="M5" t="n">
-        <v>1437.908108133742</v>
+        <v>886.1402453266331</v>
       </c>
       <c r="N5" t="n">
-        <v>1437.908108133742</v>
+        <v>1256.400245326633</v>
       </c>
       <c r="O5" t="n">
         <v>1437.908108133742</v>
@@ -4613,22 +4613,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1222.526720202428</v>
+        <v>519.734682177394</v>
       </c>
       <c r="C6" t="n">
-        <v>857.7793338938229</v>
+        <v>154.9872958687886</v>
       </c>
       <c r="D6" t="n">
-        <v>506.3271249062445</v>
+        <v>29.92</v>
       </c>
       <c r="E6" t="n">
-        <v>160.193693368959</v>
+        <v>29.92</v>
       </c>
       <c r="F6" t="n">
-        <v>160.193693368959</v>
+        <v>29.92</v>
       </c>
       <c r="G6" t="n">
-        <v>160.193693368959</v>
+        <v>29.92</v>
       </c>
       <c r="H6" t="n">
         <v>29.92</v>
@@ -4676,13 +4676,13 @@
         <v>1275.29023773295</v>
       </c>
       <c r="W6" t="n">
-        <v>1242.590093379587</v>
+        <v>897.5124599551718</v>
       </c>
       <c r="X6" t="n">
-        <v>1222.526720202428</v>
+        <v>519.734682177394</v>
       </c>
       <c r="Y6" t="n">
-        <v>1222.526720202428</v>
+        <v>519.734682177394</v>
       </c>
     </row>
     <row r="7">
@@ -4692,31 +4692,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>841.5875519028423</v>
+        <v>505.7585226289696</v>
       </c>
       <c r="C7" t="n">
-        <v>841.5875519028423</v>
+        <v>505.7585226289696</v>
       </c>
       <c r="D7" t="n">
-        <v>841.5875519028423</v>
+        <v>505.7585226289696</v>
       </c>
       <c r="E7" t="n">
-        <v>841.5875519028423</v>
+        <v>505.7585226289696</v>
       </c>
       <c r="F7" t="n">
-        <v>841.5875519028423</v>
+        <v>505.7585226289696</v>
       </c>
       <c r="G7" t="n">
-        <v>841.5875519028423</v>
+        <v>505.7585226289696</v>
       </c>
       <c r="H7" t="n">
-        <v>1012.723127881912</v>
+        <v>654.5935815663379</v>
       </c>
       <c r="I7" t="n">
-        <v>1012.723127881912</v>
+        <v>881.2025562401257</v>
       </c>
       <c r="J7" t="n">
-        <v>1382.983127881912</v>
+        <v>1251.462556240126</v>
       </c>
       <c r="K7" t="n">
         <v>1382.983127881912</v>
@@ -4752,16 +4752,16 @@
         <v>505.7585226289696</v>
       </c>
       <c r="V7" t="n">
-        <v>704.5799155149155</v>
+        <v>505.7585226289696</v>
       </c>
       <c r="W7" t="n">
-        <v>841.5875519028423</v>
+        <v>505.7585226289696</v>
       </c>
       <c r="X7" t="n">
-        <v>841.5875519028423</v>
+        <v>505.7585226289696</v>
       </c>
       <c r="Y7" t="n">
-        <v>841.5875519028423</v>
+        <v>505.7585226289696</v>
       </c>
     </row>
     <row r="8">
@@ -4771,49 +4771,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>108.731003807232</v>
+        <v>108.7310038072321</v>
       </c>
       <c r="C8" t="n">
-        <v>58.7566823496624</v>
+        <v>58.75668234966251</v>
       </c>
       <c r="D8" t="n">
-        <v>48.31309069324847</v>
+        <v>48.31309069324858</v>
       </c>
       <c r="E8" t="n">
-        <v>43.90572745398721</v>
+        <v>43.90572745398732</v>
       </c>
       <c r="F8" t="n">
-        <v>38.96670855700554</v>
+        <v>38.96670855700565</v>
       </c>
       <c r="G8" t="n">
-        <v>35.58557518755106</v>
+        <v>35.58557518755118</v>
       </c>
       <c r="H8" t="n">
-        <v>31.736856432148</v>
+        <v>29.92</v>
       </c>
       <c r="I8" t="n">
         <v>29.92</v>
       </c>
       <c r="J8" t="n">
-        <v>400.18</v>
+        <v>29.92</v>
       </c>
       <c r="K8" t="n">
-        <v>451.8183303517587</v>
+        <v>81.5583303517588</v>
       </c>
       <c r="L8" t="n">
-        <v>515.8802453266331</v>
+        <v>145.6202453266332</v>
       </c>
       <c r="M8" t="n">
         <v>515.8802453266331</v>
       </c>
       <c r="N8" t="n">
-        <v>755.48</v>
+        <v>886.1402453266331</v>
       </c>
       <c r="O8" t="n">
-        <v>755.48</v>
+        <v>886.1402453266331</v>
       </c>
       <c r="P8" t="n">
-        <v>1125.74</v>
+        <v>1256.400245326633</v>
       </c>
       <c r="Q8" t="n">
         <v>1496</v>
@@ -4828,19 +4828,19 @@
         <v>1222.884106610596</v>
       </c>
       <c r="U8" t="n">
-        <v>971.1785586019998</v>
+        <v>971.178558602</v>
       </c>
       <c r="V8" t="n">
-        <v>739.0058069183393</v>
+        <v>739.0058069183394</v>
       </c>
       <c r="W8" t="n">
-        <v>498.2245180486953</v>
+        <v>498.2245180486954</v>
       </c>
       <c r="X8" t="n">
-        <v>304.0004438460006</v>
+        <v>304.0004438460007</v>
       </c>
       <c r="Y8" t="n">
-        <v>191.5585926512467</v>
+        <v>191.5585926512468</v>
       </c>
     </row>
     <row r="9">
@@ -4850,22 +4850,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>363.3030116424684</v>
+        <v>340.4956193983517</v>
       </c>
       <c r="C9" t="n">
-        <v>363.3030116424684</v>
+        <v>340.4956193983517</v>
       </c>
       <c r="D9" t="n">
-        <v>363.3030116424684</v>
+        <v>340.4956193983517</v>
       </c>
       <c r="E9" t="n">
-        <v>363.3030116424684</v>
+        <v>29.92</v>
       </c>
       <c r="F9" t="n">
-        <v>363.3030116424684</v>
+        <v>29.92</v>
       </c>
       <c r="G9" t="n">
-        <v>363.3030116424684</v>
+        <v>29.92</v>
       </c>
       <c r="H9" t="n">
         <v>29.92</v>
@@ -4898,28 +4898,28 @@
         <v>1346.247111942856</v>
       </c>
       <c r="R9" t="n">
-        <v>1186.477229162326</v>
+        <v>1211.245105910912</v>
       </c>
       <c r="S9" t="n">
-        <v>808.6994513845481</v>
+        <v>1148.125094511552</v>
       </c>
       <c r="T9" t="n">
-        <v>430.9216736067702</v>
+        <v>1143.60646374105</v>
       </c>
       <c r="U9" t="n">
-        <v>430.7237687603838</v>
+        <v>1143.408558894664</v>
       </c>
       <c r="V9" t="n">
-        <v>416.0665291729897</v>
+        <v>1128.75131930727</v>
       </c>
       <c r="W9" t="n">
-        <v>383.3663848196276</v>
+        <v>1096.051174953907</v>
       </c>
       <c r="X9" t="n">
-        <v>363.3030116424684</v>
+        <v>718.2733971761295</v>
       </c>
       <c r="Y9" t="n">
-        <v>363.3030116424684</v>
+        <v>340.4956193983517</v>
       </c>
     </row>
     <row r="10">
@@ -4929,34 +4929,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>410.22818855586</v>
+        <v>1139.258962465079</v>
       </c>
       <c r="C10" t="n">
-        <v>514.6965880278586</v>
+        <v>1139.258962465079</v>
       </c>
       <c r="D10" t="n">
-        <v>514.6965880278586</v>
+        <v>1139.258962465079</v>
       </c>
       <c r="E10" t="n">
-        <v>632.5254922392717</v>
+        <v>1257.087866676492</v>
       </c>
       <c r="F10" t="n">
-        <v>632.5254922392717</v>
+        <v>1381.448839268427</v>
       </c>
       <c r="G10" t="n">
-        <v>786.1141532081242</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="H10" t="n">
-        <v>786.1141532081242</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="I10" t="n">
-        <v>1012.723127881912</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="J10" t="n">
-        <v>1382.983127881912</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="K10" t="n">
-        <v>1382.983127881912</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="L10" t="n">
         <v>1386.743548464727</v>
@@ -4968,10 +4968,10 @@
         <v>1149.534310393385</v>
       </c>
       <c r="O10" t="n">
-        <v>932.9209073660642</v>
+        <v>932.9209073660643</v>
       </c>
       <c r="P10" t="n">
-        <v>665.0402361121327</v>
+        <v>665.0402361121328</v>
       </c>
       <c r="Q10" t="n">
         <v>351.4672397226398</v>
@@ -4980,25 +4980,25 @@
         <v>29.92</v>
       </c>
       <c r="S10" t="n">
-        <v>70.34367574991084</v>
+        <v>70.34367574991083</v>
       </c>
       <c r="T10" t="n">
         <v>259.1973975316665</v>
       </c>
       <c r="U10" t="n">
-        <v>259.1973975316665</v>
+        <v>505.7585226289696</v>
       </c>
       <c r="V10" t="n">
-        <v>259.1973975316665</v>
+        <v>704.5799155149155</v>
       </c>
       <c r="W10" t="n">
-        <v>259.1973975316665</v>
+        <v>876.4708337745928</v>
       </c>
       <c r="X10" t="n">
-        <v>410.22818855586</v>
+        <v>1027.501624798786</v>
       </c>
       <c r="Y10" t="n">
-        <v>410.22818855586</v>
+        <v>1027.501624798786</v>
       </c>
     </row>
     <row r="11">
@@ -5008,13 +5008,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>607.5035534240029</v>
+        <v>608.2066695820786</v>
       </c>
       <c r="C11" t="n">
-        <v>475.7110501482515</v>
+        <v>476.4141663063272</v>
       </c>
       <c r="D11" t="n">
-        <v>383.4492766736557</v>
+        <v>384.1523928317314</v>
       </c>
       <c r="E11" t="n">
         <v>297.9268477742883</v>
@@ -5041,16 +5041,16 @@
         <v>983.9716941431833</v>
       </c>
       <c r="M11" t="n">
-        <v>1632.421694143183</v>
+        <v>1585.241587554807</v>
       </c>
       <c r="N11" t="n">
-        <v>1637.361628029778</v>
+        <v>2233.691587554807</v>
       </c>
       <c r="O11" t="n">
-        <v>1813.91480011625</v>
+        <v>2410.244759641279</v>
       </c>
       <c r="P11" t="n">
-        <v>2023.670040474971</v>
+        <v>2620</v>
       </c>
       <c r="Q11" t="n">
         <v>2620</v>
@@ -5074,10 +5074,10 @@
         <v>1242.451613120012</v>
       </c>
       <c r="X11" t="n">
-        <v>966.4093570991351</v>
+        <v>967.1124732572108</v>
       </c>
       <c r="Y11" t="n">
-        <v>772.1493240861994</v>
+        <v>772.852440244275</v>
       </c>
     </row>
     <row r="12">
@@ -5087,25 +5087,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>502.743697048149</v>
+        <v>1050.16013417974</v>
       </c>
       <c r="C12" t="n">
-        <v>460.2185329617658</v>
+        <v>1007.634970093357</v>
       </c>
       <c r="D12" t="n">
-        <v>430.9885461964096</v>
+        <v>978.4049833280011</v>
       </c>
       <c r="E12" t="n">
-        <v>407.0773368813464</v>
+        <v>921.1658341605817</v>
       </c>
       <c r="F12" t="n">
-        <v>386.2326476511677</v>
+        <v>578.0989227081807</v>
       </c>
       <c r="G12" t="n">
-        <v>58.00018335964018</v>
+        <v>249.8664584166532</v>
       </c>
       <c r="H12" t="n">
-        <v>52.4</v>
+        <v>244.266275057013</v>
       </c>
       <c r="I12" t="n">
         <v>52.4</v>
@@ -5135,28 +5135,28 @@
         <v>2313.990605368536</v>
       </c>
       <c r="R12" t="n">
-        <v>1907.723677356515</v>
+        <v>2132.917892265885</v>
       </c>
       <c r="S12" t="n">
-        <v>1773.479928583418</v>
+        <v>1998.674143492788</v>
       </c>
       <c r="T12" t="n">
-        <v>1689.463823065442</v>
+        <v>1914.658037974811</v>
       </c>
       <c r="U12" t="n">
-        <v>1285.26339296653</v>
+        <v>1832.679830098122</v>
       </c>
       <c r="V12" t="n">
-        <v>1188.787971560954</v>
+        <v>1736.204408692546</v>
       </c>
       <c r="W12" t="n">
-        <v>1074.26964538941</v>
+        <v>1621.686082521002</v>
       </c>
       <c r="X12" t="n">
-        <v>650.1658681718469</v>
+        <v>1519.804527525661</v>
       </c>
       <c r="Y12" t="n">
-        <v>568.9624411353476</v>
+        <v>1116.378878266939</v>
       </c>
     </row>
     <row r="13">
@@ -5166,40 +5166,40 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>673.4417775581344</v>
+        <v>673.4417775581345</v>
       </c>
       <c r="C13" t="n">
-        <v>719.2537833765701</v>
+        <v>719.2537833765703</v>
       </c>
       <c r="D13" t="n">
-        <v>752.3829275015702</v>
+        <v>752.3829275015703</v>
       </c>
       <c r="E13" t="n">
-        <v>790.0218317129832</v>
+        <v>790.0218317129833</v>
       </c>
       <c r="F13" t="n">
-        <v>834.1928043049187</v>
+        <v>834.1928043049188</v>
       </c>
       <c r="G13" t="n">
-        <v>908.0645554377056</v>
+        <v>908.0645554377057</v>
       </c>
       <c r="H13" t="n">
         <v>1003.21633305612</v>
       </c>
       <c r="I13" t="n">
-        <v>1163.862419205317</v>
+        <v>1163.862419205318</v>
       </c>
       <c r="J13" t="n">
-        <v>1491.077756743014</v>
+        <v>1491.077756743015</v>
       </c>
       <c r="K13" t="n">
         <v>1597.372803794637</v>
       </c>
       <c r="L13" t="n">
-        <v>1591.155096928856</v>
+        <v>1594.034249936398</v>
       </c>
       <c r="M13" t="n">
-        <v>1492.275360291075</v>
+        <v>1495.154513298618</v>
       </c>
       <c r="N13" t="n">
         <v>1342.71903405416</v>
@@ -5211,10 +5211,10 @@
         <v>821.1953191039224</v>
       </c>
       <c r="Q13" t="n">
-        <v>466.2233328154397</v>
+        <v>466.2233328154396</v>
       </c>
       <c r="R13" t="n">
-        <v>84.56167017509823</v>
+        <v>84.56167017509824</v>
       </c>
       <c r="S13" t="n">
         <v>52.4</v>
@@ -5223,19 +5223,19 @@
         <v>163.0851070276573</v>
       </c>
       <c r="U13" t="n">
-        <v>329.4820370429931</v>
+        <v>329.4820370429932</v>
       </c>
       <c r="V13" t="n">
         <v>448.1134299289391</v>
       </c>
       <c r="W13" t="n">
-        <v>539.8143481886165</v>
+        <v>539.8143481886166</v>
       </c>
       <c r="X13" t="n">
-        <v>610.65513921281</v>
+        <v>610.6551392128101</v>
       </c>
       <c r="Y13" t="n">
-        <v>641.8744398918423</v>
+        <v>641.8744398918424</v>
       </c>
     </row>
     <row r="14">
@@ -5269,25 +5269,25 @@
         <v>52.4</v>
       </c>
       <c r="J14" t="n">
-        <v>141.6759849731395</v>
+        <v>567.6776741934345</v>
       </c>
       <c r="K14" t="n">
-        <v>327.4727226113304</v>
+        <v>753.4744118316256</v>
       </c>
       <c r="L14" t="n">
-        <v>557.9700049228883</v>
+        <v>983.9716941431833</v>
       </c>
       <c r="M14" t="n">
-        <v>557.9700049228883</v>
+        <v>1585.241587554807</v>
       </c>
       <c r="N14" t="n">
-        <v>1206.420004922888</v>
+        <v>2233.691587554807</v>
       </c>
       <c r="O14" t="n">
-        <v>1813.91480011625</v>
+        <v>2410.244759641279</v>
       </c>
       <c r="P14" t="n">
-        <v>2023.670040474971</v>
+        <v>2620</v>
       </c>
       <c r="Q14" t="n">
         <v>2620</v>
@@ -5324,22 +5324,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1372.382356401963</v>
+        <v>502.743697048149</v>
       </c>
       <c r="C15" t="n">
-        <v>1329.85719231558</v>
+        <v>460.2185329617659</v>
       </c>
       <c r="D15" t="n">
-        <v>1075.432990640854</v>
+        <v>430.9885461964097</v>
       </c>
       <c r="E15" t="n">
-        <v>729.2995591035686</v>
+        <v>407.0773368813464</v>
       </c>
       <c r="F15" t="n">
-        <v>386.2326476511677</v>
+        <v>64.01042542894548</v>
       </c>
       <c r="G15" t="n">
-        <v>58.00018335964018</v>
+        <v>58.00018335964016</v>
       </c>
       <c r="H15" t="n">
         <v>52.4</v>
@@ -5384,16 +5384,16 @@
         <v>1832.679830098122</v>
       </c>
       <c r="V15" t="n">
-        <v>1736.204408692546</v>
+        <v>1511.010193783176</v>
       </c>
       <c r="W15" t="n">
-        <v>1621.686082521002</v>
+        <v>1074.26964538941</v>
       </c>
       <c r="X15" t="n">
-        <v>1519.804527525661</v>
+        <v>650.1658681718469</v>
       </c>
       <c r="Y15" t="n">
-        <v>1438.601100489161</v>
+        <v>568.9624411353476</v>
       </c>
     </row>
     <row r="16">
@@ -5403,55 +5403,55 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>673.4417775581344</v>
+        <v>673.4417775581345</v>
       </c>
       <c r="C16" t="n">
-        <v>719.2537833765701</v>
+        <v>719.2537833765703</v>
       </c>
       <c r="D16" t="n">
-        <v>752.3829275015702</v>
+        <v>752.3829275015726</v>
       </c>
       <c r="E16" t="n">
-        <v>790.0218317129832</v>
+        <v>790.0218317129855</v>
       </c>
       <c r="F16" t="n">
-        <v>834.1928043049187</v>
+        <v>834.1928043049211</v>
       </c>
       <c r="G16" t="n">
-        <v>908.0645554377056</v>
+        <v>908.064555437708</v>
       </c>
       <c r="H16" t="n">
-        <v>1003.21633305612</v>
+        <v>1003.216333056122</v>
       </c>
       <c r="I16" t="n">
-        <v>1163.862419205317</v>
+        <v>1163.86241920532</v>
       </c>
       <c r="J16" t="n">
-        <v>1491.077756743014</v>
+        <v>1491.077756743017</v>
       </c>
       <c r="K16" t="n">
-        <v>1597.372803794637</v>
+        <v>1597.37280379464</v>
       </c>
       <c r="L16" t="n">
-        <v>1591.155096928856</v>
+        <v>1591.155096928858</v>
       </c>
       <c r="M16" t="n">
-        <v>1492.275360291075</v>
+        <v>1492.275360291078</v>
       </c>
       <c r="N16" t="n">
-        <v>1339.839881046618</v>
+        <v>1339.839881046621</v>
       </c>
       <c r="O16" t="n">
-        <v>1112.514307960106</v>
+        <v>1109.635154952567</v>
       </c>
       <c r="P16" t="n">
-        <v>821.1953191039224</v>
+        <v>818.316166096383</v>
       </c>
       <c r="Q16" t="n">
-        <v>466.2233328154397</v>
+        <v>463.3441798079002</v>
       </c>
       <c r="R16" t="n">
-        <v>84.56167017509823</v>
+        <v>81.68251716755879</v>
       </c>
       <c r="S16" t="n">
         <v>52.4</v>
@@ -5460,19 +5460,19 @@
         <v>163.0851070276573</v>
       </c>
       <c r="U16" t="n">
-        <v>329.4820370429931</v>
+        <v>329.4820370429932</v>
       </c>
       <c r="V16" t="n">
         <v>448.1134299289391</v>
       </c>
       <c r="W16" t="n">
-        <v>539.8143481886165</v>
+        <v>539.8143481886166</v>
       </c>
       <c r="X16" t="n">
-        <v>610.65513921281</v>
+        <v>610.6551392128101</v>
       </c>
       <c r="Y16" t="n">
-        <v>641.8744398918423</v>
+        <v>641.8744398918424</v>
       </c>
     </row>
     <row r="17">
@@ -5515,16 +5515,16 @@
         <v>983.9716941431833</v>
       </c>
       <c r="M17" t="n">
-        <v>988.9116280297778</v>
+        <v>983.9716941431834</v>
       </c>
       <c r="N17" t="n">
-        <v>1637.361628029778</v>
+        <v>1632.421694143184</v>
       </c>
       <c r="O17" t="n">
-        <v>1813.91480011625</v>
+        <v>2280.871694143184</v>
       </c>
       <c r="P17" t="n">
-        <v>2023.670040474971</v>
+        <v>2490.626934501905</v>
       </c>
       <c r="Q17" t="n">
         <v>2620</v>
@@ -5561,13 +5561,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1147.188141492594</v>
+        <v>180.5214748259267</v>
       </c>
       <c r="C18" t="n">
-        <v>782.4407551839881</v>
+        <v>137.9963107395436</v>
       </c>
       <c r="D18" t="n">
-        <v>430.9885461964096</v>
+        <v>108.7663239741874</v>
       </c>
       <c r="E18" t="n">
         <v>84.85511465912413</v>
@@ -5621,16 +5621,16 @@
         <v>1832.679830098122</v>
       </c>
       <c r="V18" t="n">
-        <v>1736.204408692546</v>
+        <v>1413.982186470323</v>
       </c>
       <c r="W18" t="n">
-        <v>1621.686082521002</v>
+        <v>977.2416380765571</v>
       </c>
       <c r="X18" t="n">
-        <v>1519.804527525661</v>
+        <v>553.1378608589939</v>
       </c>
       <c r="Y18" t="n">
-        <v>1438.601100489161</v>
+        <v>246.7402189131253</v>
       </c>
     </row>
     <row r="19">
@@ -5646,49 +5646,49 @@
         <v>719.2537833765703</v>
       </c>
       <c r="D19" t="n">
-        <v>752.3829275015703</v>
+        <v>752.3829275015728</v>
       </c>
       <c r="E19" t="n">
-        <v>790.0218317129833</v>
+        <v>790.0218317129858</v>
       </c>
       <c r="F19" t="n">
-        <v>834.1928043049188</v>
+        <v>834.1928043049213</v>
       </c>
       <c r="G19" t="n">
-        <v>908.0645554377057</v>
+        <v>908.0645554377082</v>
       </c>
       <c r="H19" t="n">
-        <v>1003.21633305612</v>
+        <v>1003.216333056122</v>
       </c>
       <c r="I19" t="n">
-        <v>1163.862419205318</v>
+        <v>1163.86241920532</v>
       </c>
       <c r="J19" t="n">
-        <v>1491.077756743015</v>
+        <v>1491.077756743017</v>
       </c>
       <c r="K19" t="n">
-        <v>1597.372803794637</v>
+        <v>1597.37280379464</v>
       </c>
       <c r="L19" t="n">
-        <v>1591.155096928856</v>
+        <v>1591.155096928858</v>
       </c>
       <c r="M19" t="n">
-        <v>1492.275360291076</v>
+        <v>1492.275360291078</v>
       </c>
       <c r="N19" t="n">
-        <v>1339.839881046618</v>
+        <v>1339.839881046621</v>
       </c>
       <c r="O19" t="n">
-        <v>1109.635154952564</v>
+        <v>1109.635154952567</v>
       </c>
       <c r="P19" t="n">
-        <v>818.3161660963807</v>
+        <v>818.316166096383</v>
       </c>
       <c r="Q19" t="n">
-        <v>463.3441798078979</v>
+        <v>463.3441798079002</v>
       </c>
       <c r="R19" t="n">
-        <v>81.68251716755651</v>
+        <v>81.68251716755879</v>
       </c>
       <c r="S19" t="n">
         <v>52.4</v>
@@ -5719,7 +5719,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>608.2066695820786</v>
+        <v>607.5035534240029</v>
       </c>
       <c r="C20" t="n">
         <v>476.4141663063272</v>
@@ -5743,25 +5743,25 @@
         <v>52.4</v>
       </c>
       <c r="J20" t="n">
-        <v>141.6759849731395</v>
+        <v>567.6776741934345</v>
       </c>
       <c r="K20" t="n">
-        <v>327.4727226113304</v>
+        <v>753.4744118316256</v>
       </c>
       <c r="L20" t="n">
-        <v>936.7915875548069</v>
+        <v>983.9716941431833</v>
       </c>
       <c r="M20" t="n">
-        <v>1585.241587554807</v>
+        <v>988.9116280297774</v>
       </c>
       <c r="N20" t="n">
-        <v>2233.691587554807</v>
+        <v>1637.361628029778</v>
       </c>
       <c r="O20" t="n">
-        <v>2410.244759641279</v>
+        <v>1813.91480011625</v>
       </c>
       <c r="P20" t="n">
-        <v>2620</v>
+        <v>2023.670040474971</v>
       </c>
       <c r="Q20" t="n">
         <v>2620</v>
@@ -5770,25 +5770,25 @@
         <v>2620</v>
       </c>
       <c r="S20" t="n">
-        <v>2477.038452472668</v>
+        <v>2476.335336314592</v>
       </c>
       <c r="T20" t="n">
-        <v>2213.182776293874</v>
+        <v>2212.479660135798</v>
       </c>
       <c r="U20" t="n">
-        <v>1879.745133467756</v>
+        <v>1879.04201730968</v>
       </c>
       <c r="V20" t="n">
-        <v>1565.754199965913</v>
+        <v>1565.051083807838</v>
       </c>
       <c r="W20" t="n">
-        <v>1243.154729278087</v>
+        <v>1242.451613120012</v>
       </c>
       <c r="X20" t="n">
-        <v>967.1124732572108</v>
+        <v>966.4093570991351</v>
       </c>
       <c r="Y20" t="n">
-        <v>772.852440244275</v>
+        <v>772.1493240861994</v>
       </c>
     </row>
     <row r="21">
@@ -5798,16 +5798,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1050.16013417974</v>
+        <v>1147.188141492594</v>
       </c>
       <c r="C21" t="n">
-        <v>685.412747871135</v>
+        <v>782.4407551839881</v>
       </c>
       <c r="D21" t="n">
-        <v>430.9885461964096</v>
+        <v>430.9885461964097</v>
       </c>
       <c r="E21" t="n">
-        <v>84.85511465912413</v>
+        <v>407.0773368813464</v>
       </c>
       <c r="F21" t="n">
         <v>64.01042542894548</v>
@@ -5877,55 +5877,55 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>673.4417775581344</v>
+        <v>673.4417775581362</v>
       </c>
       <c r="C22" t="n">
-        <v>719.2537833765701</v>
+        <v>719.253783376572</v>
       </c>
       <c r="D22" t="n">
-        <v>752.3829275015702</v>
+        <v>752.382927501572</v>
       </c>
       <c r="E22" t="n">
-        <v>790.0218317129832</v>
+        <v>790.021831712985</v>
       </c>
       <c r="F22" t="n">
-        <v>834.1928043049187</v>
+        <v>834.1928043049205</v>
       </c>
       <c r="G22" t="n">
-        <v>908.0645554377056</v>
+        <v>908.0645554377074</v>
       </c>
       <c r="H22" t="n">
-        <v>1003.21633305612</v>
+        <v>1003.216333056121</v>
       </c>
       <c r="I22" t="n">
-        <v>1163.862419205317</v>
+        <v>1163.862419205319</v>
       </c>
       <c r="J22" t="n">
-        <v>1491.077756743014</v>
+        <v>1491.077756743016</v>
       </c>
       <c r="K22" t="n">
-        <v>1597.372803794637</v>
+        <v>1597.372803794639</v>
       </c>
       <c r="L22" t="n">
-        <v>1591.155096928856</v>
+        <v>1591.155096928857</v>
       </c>
       <c r="M22" t="n">
-        <v>1492.275360291075</v>
+        <v>1492.275360291077</v>
       </c>
       <c r="N22" t="n">
-        <v>1339.839881046618</v>
+        <v>1339.83988104662</v>
       </c>
       <c r="O22" t="n">
-        <v>1109.635154952564</v>
+        <v>1109.635154952566</v>
       </c>
       <c r="P22" t="n">
-        <v>821.1953191039224</v>
+        <v>818.3161660963825</v>
       </c>
       <c r="Q22" t="n">
-        <v>466.2233328154397</v>
+        <v>463.3441798078997</v>
       </c>
       <c r="R22" t="n">
-        <v>84.56167017509823</v>
+        <v>81.68251716755827</v>
       </c>
       <c r="S22" t="n">
         <v>52.4</v>
@@ -5946,7 +5946,7 @@
         <v>610.65513921281</v>
       </c>
       <c r="Y22" t="n">
-        <v>641.8744398918423</v>
+        <v>641.8744398918441</v>
       </c>
     </row>
     <row r="23">
@@ -5956,19 +5956,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>608.2066695820786</v>
+        <v>607.5035534240029</v>
       </c>
       <c r="C23" t="n">
-        <v>476.4141663063272</v>
+        <v>475.7110501482515</v>
       </c>
       <c r="D23" t="n">
-        <v>384.1523928317314</v>
+        <v>383.4492766736557</v>
       </c>
       <c r="E23" t="n">
-        <v>297.9268477742883</v>
+        <v>297.2237316162127</v>
       </c>
       <c r="F23" t="n">
-        <v>211.1696470591248</v>
+        <v>210.4665309010492</v>
       </c>
       <c r="G23" t="n">
         <v>127.0464193797368</v>
@@ -5980,52 +5980,52 @@
         <v>52.4</v>
       </c>
       <c r="J23" t="n">
-        <v>567.6776741934345</v>
+        <v>141.6759849731395</v>
       </c>
       <c r="K23" t="n">
-        <v>1216.127674193434</v>
+        <v>758.4143457182196</v>
       </c>
       <c r="L23" t="n">
-        <v>1585.241587554807</v>
+        <v>988.9116280297774</v>
       </c>
       <c r="M23" t="n">
-        <v>1585.241587554807</v>
+        <v>1637.361628029778</v>
       </c>
       <c r="N23" t="n">
-        <v>2233.691587554807</v>
+        <v>1637.361628029778</v>
       </c>
       <c r="O23" t="n">
-        <v>2410.244759641279</v>
+        <v>1813.91480011625</v>
       </c>
       <c r="P23" t="n">
-        <v>2620</v>
+        <v>2023.670040474971</v>
       </c>
       <c r="Q23" t="n">
         <v>2620</v>
       </c>
       <c r="R23" t="n">
-        <v>2620.00000000008</v>
+        <v>2620</v>
       </c>
       <c r="S23" t="n">
-        <v>2477.038452472668</v>
+        <v>2476.335336314592</v>
       </c>
       <c r="T23" t="n">
-        <v>2213.182776293874</v>
+        <v>2212.479660135798</v>
       </c>
       <c r="U23" t="n">
-        <v>1879.745133467756</v>
+        <v>1879.04201730968</v>
       </c>
       <c r="V23" t="n">
-        <v>1565.754199965913</v>
+        <v>1565.051083807838</v>
       </c>
       <c r="W23" t="n">
-        <v>1243.154729278087</v>
+        <v>1242.451613120012</v>
       </c>
       <c r="X23" t="n">
-        <v>967.1124732572108</v>
+        <v>966.4093570991351</v>
       </c>
       <c r="Y23" t="n">
-        <v>772.852440244275</v>
+        <v>772.1493240861994</v>
       </c>
     </row>
     <row r="24">
@@ -6035,19 +6035,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1147.188141492593</v>
+        <v>654.893943026788</v>
       </c>
       <c r="C24" t="n">
-        <v>1104.66297740621</v>
+        <v>612.3687789404048</v>
       </c>
       <c r="D24" t="n">
-        <v>753.2107684186319</v>
+        <v>583.1387921750486</v>
       </c>
       <c r="E24" t="n">
-        <v>407.0773368813464</v>
+        <v>559.2275828599853</v>
       </c>
       <c r="F24" t="n">
-        <v>64.01042542894548</v>
+        <v>386.2326476511677</v>
       </c>
       <c r="G24" t="n">
         <v>58.00018335964016</v>
@@ -6080,31 +6080,31 @@
         <v>2313.990605368536</v>
       </c>
       <c r="Q24" t="n">
-        <v>2313.990605368536</v>
+        <v>2240.946636437805</v>
       </c>
       <c r="R24" t="n">
-        <v>2132.917892265885</v>
+        <v>1737.651701112932</v>
       </c>
       <c r="S24" t="n">
-        <v>1773.479928583418</v>
+        <v>1603.407952339835</v>
       </c>
       <c r="T24" t="n">
-        <v>1689.463823065442</v>
+        <v>1519.391846821859</v>
       </c>
       <c r="U24" t="n">
-        <v>1607.485615188752</v>
+        <v>1115.191416722947</v>
       </c>
       <c r="V24" t="n">
-        <v>1511.010193783176</v>
+        <v>1018.715995317371</v>
       </c>
       <c r="W24" t="n">
-        <v>1396.491867611632</v>
+        <v>904.1976691458268</v>
       </c>
       <c r="X24" t="n">
-        <v>1294.610312616291</v>
+        <v>802.3161141504859</v>
       </c>
       <c r="Y24" t="n">
-        <v>1213.406885579792</v>
+        <v>721.1126871139866</v>
       </c>
     </row>
     <row r="25">
@@ -6147,22 +6147,22 @@
         <v>1591.155096928856</v>
       </c>
       <c r="M25" t="n">
-        <v>1492.275360291076</v>
+        <v>1495.154513298618</v>
       </c>
       <c r="N25" t="n">
-        <v>1339.839881046618</v>
+        <v>1342.71903405416</v>
       </c>
       <c r="O25" t="n">
-        <v>1109.635154952564</v>
+        <v>1112.514307960106</v>
       </c>
       <c r="P25" t="n">
-        <v>818.3161660963807</v>
+        <v>821.1953191039224</v>
       </c>
       <c r="Q25" t="n">
-        <v>463.3441798078979</v>
+        <v>466.2233328154396</v>
       </c>
       <c r="R25" t="n">
-        <v>81.68251716755651</v>
+        <v>84.56167017509824</v>
       </c>
       <c r="S25" t="n">
         <v>52.4</v>
@@ -6193,76 +6193,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>607.5035534241634</v>
+        <v>608.2066695820798</v>
       </c>
       <c r="C26" t="n">
-        <v>475.711050148412</v>
+        <v>476.4141663063284</v>
       </c>
       <c r="D26" t="n">
-        <v>383.4492766738163</v>
+        <v>384.1523928317326</v>
       </c>
       <c r="E26" t="n">
-        <v>297.2237316163732</v>
+        <v>297.9268477742895</v>
       </c>
       <c r="F26" t="n">
-        <v>210.4665309012097</v>
+        <v>211.169647059126</v>
       </c>
       <c r="G26" t="n">
-        <v>127.0464193797401</v>
+        <v>127.046419379738</v>
       </c>
       <c r="H26" t="n">
-        <v>52.40000000000321</v>
+        <v>52.40000000000117</v>
       </c>
       <c r="I26" t="n">
-        <v>52.40000000000321</v>
+        <v>52.40000000000117</v>
       </c>
       <c r="J26" t="n">
-        <v>567.6776741934377</v>
+        <v>567.6776741934357</v>
       </c>
       <c r="K26" t="n">
-        <v>753.4744118316287</v>
+        <v>753.4744118316266</v>
       </c>
       <c r="L26" t="n">
-        <v>983.9716941431865</v>
+        <v>1401.924411831641</v>
       </c>
       <c r="M26" t="n">
-        <v>1632.421694143199</v>
+        <v>1637.361628029837</v>
       </c>
       <c r="N26" t="n">
-        <v>1637.361628029938</v>
+        <v>1637.361628029837</v>
       </c>
       <c r="O26" t="n">
-        <v>1813.914800116411</v>
+        <v>1813.914800116309</v>
       </c>
       <c r="P26" t="n">
-        <v>2023.670040475131</v>
+        <v>2023.67004047503</v>
       </c>
       <c r="Q26" t="n">
-        <v>2620.000000000161</v>
+        <v>2620.000000000059</v>
       </c>
       <c r="R26" t="n">
-        <v>2620.000000000161</v>
+        <v>2620.000000000059</v>
       </c>
       <c r="S26" t="n">
-        <v>2476.335336314753</v>
+        <v>2476.335336314651</v>
       </c>
       <c r="T26" t="n">
-        <v>2212.479660135959</v>
+        <v>2212.479660135857</v>
       </c>
       <c r="U26" t="n">
-        <v>1879.042017309841</v>
+        <v>1879.042017309739</v>
       </c>
       <c r="V26" t="n">
-        <v>1565.051083807998</v>
+        <v>1565.051083807896</v>
       </c>
       <c r="W26" t="n">
-        <v>1242.451613120172</v>
+        <v>1242.45161312007</v>
       </c>
       <c r="X26" t="n">
-        <v>966.4093570992957</v>
+        <v>967.1124732572121</v>
       </c>
       <c r="Y26" t="n">
-        <v>772.1493240863599</v>
+        <v>772.8524402442763</v>
       </c>
     </row>
     <row r="27">
@@ -6272,76 +6272,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>502.7436970481522</v>
+        <v>694.6099721051633</v>
       </c>
       <c r="C27" t="n">
-        <v>460.2185329617691</v>
+        <v>652.0848080187801</v>
       </c>
       <c r="D27" t="n">
-        <v>430.9885461964129</v>
+        <v>622.8548212534239</v>
       </c>
       <c r="E27" t="n">
-        <v>407.0773368813496</v>
+        <v>598.9436119383606</v>
       </c>
       <c r="F27" t="n">
-        <v>64.01042542894869</v>
+        <v>578.0989227081819</v>
       </c>
       <c r="G27" t="n">
-        <v>58.00018335964339</v>
+        <v>249.8664584166544</v>
       </c>
       <c r="H27" t="n">
-        <v>52.40000000000321</v>
+        <v>244.2662750570142</v>
       </c>
       <c r="I27" t="n">
-        <v>52.40000000000321</v>
+        <v>52.40000000000117</v>
       </c>
       <c r="J27" t="n">
-        <v>250.1913459300192</v>
+        <v>250.1913459300171</v>
       </c>
       <c r="K27" t="n">
-        <v>565.5796394772328</v>
+        <v>565.5796394772308</v>
       </c>
       <c r="L27" t="n">
-        <v>1006.615493996961</v>
+        <v>1006.615493996959</v>
       </c>
       <c r="M27" t="n">
-        <v>1290.71088573982</v>
+        <v>1290.710885739818</v>
       </c>
       <c r="N27" t="n">
-        <v>1627.246884215313</v>
+        <v>1627.246884215311</v>
       </c>
       <c r="O27" t="n">
-        <v>2052.228604861296</v>
+        <v>2052.228604861294</v>
       </c>
       <c r="P27" t="n">
-        <v>2313.990605368539</v>
+        <v>2313.990605368537</v>
       </c>
       <c r="Q27" t="n">
-        <v>2240.946636437809</v>
+        <v>2240.946636437806</v>
       </c>
       <c r="R27" t="n">
-        <v>1737.651701112935</v>
+        <v>1737.651701112933</v>
       </c>
       <c r="S27" t="n">
-        <v>1281.185730117616</v>
+        <v>1603.407952339836</v>
       </c>
       <c r="T27" t="n">
-        <v>1197.169624599639</v>
+        <v>1519.391846821859</v>
       </c>
       <c r="U27" t="n">
-        <v>1115.19141672295</v>
+        <v>1437.41363894517</v>
       </c>
       <c r="V27" t="n">
-        <v>866.565749338735</v>
+        <v>1058.432024395746</v>
       </c>
       <c r="W27" t="n">
-        <v>752.047423167191</v>
+        <v>943.9136982242021</v>
       </c>
       <c r="X27" t="n">
-        <v>650.1658681718501</v>
+        <v>842.0321432288612</v>
       </c>
       <c r="Y27" t="n">
-        <v>568.9624411353508</v>
+        <v>760.8287161923619</v>
       </c>
     </row>
     <row r="28">
@@ -6351,76 +6351,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>673.4417775581377</v>
+        <v>673.4417775581356</v>
       </c>
       <c r="C28" t="n">
-        <v>719.2537833765734</v>
+        <v>719.2537833765714</v>
       </c>
       <c r="D28" t="n">
-        <v>752.3829275015735</v>
+        <v>752.3829275015714</v>
       </c>
       <c r="E28" t="n">
-        <v>790.0218317129865</v>
+        <v>790.0218317129844</v>
       </c>
       <c r="F28" t="n">
-        <v>834.192804304922</v>
+        <v>834.1928043049199</v>
       </c>
       <c r="G28" t="n">
-        <v>908.0645554377089</v>
+        <v>908.0645554377069</v>
       </c>
       <c r="H28" t="n">
-        <v>1003.216333056123</v>
+        <v>1003.216333056121</v>
       </c>
       <c r="I28" t="n">
-        <v>1163.862419205321</v>
+        <v>1163.862419205318</v>
       </c>
       <c r="J28" t="n">
-        <v>1491.077756743018</v>
+        <v>1491.077756743016</v>
       </c>
       <c r="K28" t="n">
-        <v>1597.372803794641</v>
+        <v>1597.372803794638</v>
       </c>
       <c r="L28" t="n">
-        <v>1591.155096928859</v>
+        <v>1591.155096928857</v>
       </c>
       <c r="M28" t="n">
-        <v>1492.275360291079</v>
+        <v>1492.275360291077</v>
       </c>
       <c r="N28" t="n">
-        <v>1339.839881046622</v>
+        <v>1342.719034054161</v>
       </c>
       <c r="O28" t="n">
-        <v>1109.635154952568</v>
+        <v>1112.514307960107</v>
       </c>
       <c r="P28" t="n">
-        <v>818.3161660963843</v>
+        <v>821.1953191039236</v>
       </c>
       <c r="Q28" t="n">
-        <v>463.3441798079015</v>
+        <v>466.2233328154408</v>
       </c>
       <c r="R28" t="n">
-        <v>81.68251716756009</v>
+        <v>84.56167017509941</v>
       </c>
       <c r="S28" t="n">
-        <v>52.40000000000321</v>
+        <v>52.40000000000117</v>
       </c>
       <c r="T28" t="n">
-        <v>163.0851070276605</v>
+        <v>163.0851070276585</v>
       </c>
       <c r="U28" t="n">
-        <v>329.4820370429964</v>
+        <v>329.4820370429943</v>
       </c>
       <c r="V28" t="n">
-        <v>448.1134299289423</v>
+        <v>448.1134299289403</v>
       </c>
       <c r="W28" t="n">
-        <v>539.8143481886198</v>
+        <v>539.8143481886177</v>
       </c>
       <c r="X28" t="n">
-        <v>610.6551392128133</v>
+        <v>610.6551392128113</v>
       </c>
       <c r="Y28" t="n">
-        <v>641.8744398918456</v>
+        <v>641.8744398918435</v>
       </c>
     </row>
     <row r="29">
@@ -6430,76 +6430,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>607.5035534240861</v>
+        <v>608.2066695820797</v>
       </c>
       <c r="C29" t="n">
-        <v>475.7110501483347</v>
+        <v>476.4141663063283</v>
       </c>
       <c r="D29" t="n">
-        <v>383.449276673739</v>
+        <v>384.1523928317325</v>
       </c>
       <c r="E29" t="n">
-        <v>297.2237316162959</v>
+        <v>297.9268477742895</v>
       </c>
       <c r="F29" t="n">
-        <v>210.4665309011324</v>
+        <v>211.169647059126</v>
       </c>
       <c r="G29" t="n">
-        <v>127.0464193797401</v>
+        <v>127.046419379738</v>
       </c>
       <c r="H29" t="n">
-        <v>52.40000000000321</v>
+        <v>52.40000000000117</v>
       </c>
       <c r="I29" t="n">
-        <v>52.40000000000321</v>
+        <v>52.40000000000117</v>
       </c>
       <c r="J29" t="n">
-        <v>141.6759849731427</v>
+        <v>567.6776741934357</v>
       </c>
       <c r="K29" t="n">
-        <v>327.4727226113337</v>
+        <v>753.4744118316266</v>
       </c>
       <c r="L29" t="n">
-        <v>557.9700049228915</v>
+        <v>983.9716941431844</v>
       </c>
       <c r="M29" t="n">
-        <v>557.9700049228915</v>
+        <v>1632.421694143187</v>
       </c>
       <c r="N29" t="n">
-        <v>1206.420004922912</v>
+        <v>1632.421694143187</v>
       </c>
       <c r="O29" t="n">
-        <v>1854.870004922932</v>
+        <v>2280.87169414319</v>
       </c>
       <c r="P29" t="n">
-        <v>2503.320004922952</v>
+        <v>2490.626934501911</v>
       </c>
       <c r="Q29" t="n">
-        <v>2620.000000000083</v>
+        <v>2620.000000000019</v>
       </c>
       <c r="R29" t="n">
-        <v>2620.000000000083</v>
+        <v>2620.000000000019</v>
       </c>
       <c r="S29" t="n">
-        <v>2476.335336314675</v>
+        <v>2477.038452472669</v>
       </c>
       <c r="T29" t="n">
-        <v>2212.479660135881</v>
+        <v>2213.182776293875</v>
       </c>
       <c r="U29" t="n">
-        <v>1879.042017309763</v>
+        <v>1879.745133467757</v>
       </c>
       <c r="V29" t="n">
-        <v>1565.051083807921</v>
+        <v>1565.754199965914</v>
       </c>
       <c r="W29" t="n">
-        <v>1242.451613120095</v>
+        <v>1243.154729278088</v>
       </c>
       <c r="X29" t="n">
-        <v>966.4093570992184</v>
+        <v>967.1124732572119</v>
       </c>
       <c r="Y29" t="n">
-        <v>772.1493240862826</v>
+        <v>772.8524402442762</v>
       </c>
     </row>
     <row r="30">
@@ -6509,76 +6509,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1147.188141492597</v>
+        <v>1372.382356401964</v>
       </c>
       <c r="C30" t="n">
-        <v>1104.662977406213</v>
+        <v>1329.857192315581</v>
       </c>
       <c r="D30" t="n">
-        <v>753.2107684186351</v>
+        <v>1075.432990640855</v>
       </c>
       <c r="E30" t="n">
-        <v>407.0773368813496</v>
+        <v>729.2995591035699</v>
       </c>
       <c r="F30" t="n">
-        <v>386.232647651171</v>
+        <v>386.2326476511689</v>
       </c>
       <c r="G30" t="n">
-        <v>380.2224055818656</v>
+        <v>380.2224055818636</v>
       </c>
       <c r="H30" t="n">
-        <v>52.40000000000321</v>
+        <v>52.40000000000117</v>
       </c>
       <c r="I30" t="n">
-        <v>52.40000000000321</v>
+        <v>52.40000000000117</v>
       </c>
       <c r="J30" t="n">
-        <v>250.1913459300192</v>
+        <v>250.1913459300171</v>
       </c>
       <c r="K30" t="n">
-        <v>565.5796394772328</v>
+        <v>565.5796394772308</v>
       </c>
       <c r="L30" t="n">
-        <v>1006.615493996961</v>
+        <v>1006.615493996959</v>
       </c>
       <c r="M30" t="n">
-        <v>1290.71088573982</v>
+        <v>1290.710885739818</v>
       </c>
       <c r="N30" t="n">
-        <v>1627.246884215313</v>
+        <v>1627.246884215311</v>
       </c>
       <c r="O30" t="n">
-        <v>2052.228604861296</v>
+        <v>2052.228604861294</v>
       </c>
       <c r="P30" t="n">
-        <v>2313.990605368539</v>
+        <v>2313.990605368537</v>
       </c>
       <c r="Q30" t="n">
-        <v>2313.990605368539</v>
+        <v>2313.990605368537</v>
       </c>
       <c r="R30" t="n">
-        <v>2132.917892265888</v>
+        <v>2132.917892265886</v>
       </c>
       <c r="S30" t="n">
-        <v>1998.674143492791</v>
+        <v>1998.674143492789</v>
       </c>
       <c r="T30" t="n">
-        <v>1689.463823065445</v>
+        <v>1914.658037974812</v>
       </c>
       <c r="U30" t="n">
-        <v>1607.485615188755</v>
+        <v>1832.679830098122</v>
       </c>
       <c r="V30" t="n">
-        <v>1511.010193783179</v>
+        <v>1736.204408692547</v>
       </c>
       <c r="W30" t="n">
-        <v>1396.491867611635</v>
+        <v>1621.686082521003</v>
       </c>
       <c r="X30" t="n">
-        <v>1294.610312616294</v>
+        <v>1519.804527525662</v>
       </c>
       <c r="Y30" t="n">
-        <v>1213.406885579795</v>
+        <v>1438.601100489162</v>
       </c>
     </row>
     <row r="31">
@@ -6588,76 +6588,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>673.4417775581377</v>
+        <v>673.4417775581356</v>
       </c>
       <c r="C31" t="n">
-        <v>719.2537833765734</v>
+        <v>719.2537833765714</v>
       </c>
       <c r="D31" t="n">
-        <v>752.3829275015735</v>
+        <v>752.3829275015714</v>
       </c>
       <c r="E31" t="n">
-        <v>790.0218317129865</v>
+        <v>790.0218317129844</v>
       </c>
       <c r="F31" t="n">
-        <v>834.192804304922</v>
+        <v>834.1928043049199</v>
       </c>
       <c r="G31" t="n">
-        <v>908.0645554377089</v>
+        <v>908.0645554377069</v>
       </c>
       <c r="H31" t="n">
-        <v>1003.216333056123</v>
+        <v>1003.216333056121</v>
       </c>
       <c r="I31" t="n">
-        <v>1163.862419205321</v>
+        <v>1163.862419205318</v>
       </c>
       <c r="J31" t="n">
-        <v>1491.077756743018</v>
+        <v>1491.077756743016</v>
       </c>
       <c r="K31" t="n">
-        <v>1597.372803794641</v>
+        <v>1597.372803794638</v>
       </c>
       <c r="L31" t="n">
-        <v>1594.034249936401</v>
+        <v>1591.155096928857</v>
       </c>
       <c r="M31" t="n">
-        <v>1495.154513298621</v>
+        <v>1492.275360291077</v>
       </c>
       <c r="N31" t="n">
-        <v>1342.719034054163</v>
+        <v>1339.839881046619</v>
       </c>
       <c r="O31" t="n">
-        <v>1112.514307960109</v>
+        <v>1109.635154952565</v>
       </c>
       <c r="P31" t="n">
-        <v>821.1953191039256</v>
+        <v>818.3161660963816</v>
       </c>
       <c r="Q31" t="n">
-        <v>466.2233328154429</v>
+        <v>466.2233328154408</v>
       </c>
       <c r="R31" t="n">
-        <v>84.56167017510144</v>
+        <v>84.56167017509942</v>
       </c>
       <c r="S31" t="n">
-        <v>52.40000000000321</v>
+        <v>52.40000000000117</v>
       </c>
       <c r="T31" t="n">
-        <v>163.0851070276605</v>
+        <v>163.0851070276585</v>
       </c>
       <c r="U31" t="n">
-        <v>329.4820370429964</v>
+        <v>329.4820370429943</v>
       </c>
       <c r="V31" t="n">
-        <v>448.1134299289423</v>
+        <v>448.1134299289403</v>
       </c>
       <c r="W31" t="n">
-        <v>539.8143481886198</v>
+        <v>539.8143481886177</v>
       </c>
       <c r="X31" t="n">
-        <v>610.6551392128133</v>
+        <v>610.6551392128113</v>
       </c>
       <c r="Y31" t="n">
-        <v>641.8744398918456</v>
+        <v>641.8744398918435</v>
       </c>
     </row>
     <row r="32">
@@ -6667,76 +6667,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>607.5035534241634</v>
+        <v>608.2066695820797</v>
       </c>
       <c r="C32" t="n">
-        <v>475.711050148412</v>
+        <v>476.4141663063283</v>
       </c>
       <c r="D32" t="n">
-        <v>383.4492766738163</v>
+        <v>384.1523928317325</v>
       </c>
       <c r="E32" t="n">
-        <v>297.2237316163732</v>
+        <v>297.9268477742895</v>
       </c>
       <c r="F32" t="n">
-        <v>210.4665309012097</v>
+        <v>211.169647059126</v>
       </c>
       <c r="G32" t="n">
-        <v>127.0464193797401</v>
+        <v>127.046419379738</v>
       </c>
       <c r="H32" t="n">
-        <v>52.40000000000321</v>
+        <v>52.40000000000117</v>
       </c>
       <c r="I32" t="n">
-        <v>52.40000000000321</v>
+        <v>52.40000000000117</v>
       </c>
       <c r="J32" t="n">
-        <v>567.6776741934377</v>
+        <v>567.6776741934357</v>
       </c>
       <c r="K32" t="n">
-        <v>753.4744118316287</v>
+        <v>753.4744118316266</v>
       </c>
       <c r="L32" t="n">
-        <v>983.9716941431865</v>
+        <v>983.9716941431844</v>
       </c>
       <c r="M32" t="n">
-        <v>1632.421694143219</v>
+        <v>1632.421694143188</v>
       </c>
       <c r="N32" t="n">
-        <v>2233.691587554968</v>
+        <v>2233.691587554866</v>
       </c>
       <c r="O32" t="n">
-        <v>2410.24475964144</v>
+        <v>2410.244759641338</v>
       </c>
       <c r="P32" t="n">
-        <v>2620.000000000161</v>
+        <v>2620.000000000059</v>
       </c>
       <c r="Q32" t="n">
-        <v>2620.000000000161</v>
+        <v>2620.000000000059</v>
       </c>
       <c r="R32" t="n">
-        <v>2620.000000000161</v>
+        <v>2620.000000000059</v>
       </c>
       <c r="S32" t="n">
-        <v>2476.335336314753</v>
+        <v>2477.038452472669</v>
       </c>
       <c r="T32" t="n">
-        <v>2212.479660135959</v>
+        <v>2213.182776293875</v>
       </c>
       <c r="U32" t="n">
-        <v>1879.042017309841</v>
+        <v>1879.745133467757</v>
       </c>
       <c r="V32" t="n">
-        <v>1565.051083807998</v>
+        <v>1565.754199965914</v>
       </c>
       <c r="W32" t="n">
-        <v>1242.451613120172</v>
+        <v>1243.154729278088</v>
       </c>
       <c r="X32" t="n">
-        <v>966.4093570992957</v>
+        <v>967.1124732572119</v>
       </c>
       <c r="Y32" t="n">
-        <v>772.1493240863599</v>
+        <v>772.8524402442762</v>
       </c>
     </row>
     <row r="33">
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>727.9379119575215</v>
+        <v>654.8939430267887</v>
       </c>
       <c r="C33" t="n">
-        <v>685.4127478711383</v>
+        <v>612.3687789404056</v>
       </c>
       <c r="D33" t="n">
-        <v>656.1827611057821</v>
+        <v>583.1387921750494</v>
       </c>
       <c r="E33" t="n">
-        <v>632.2715517907188</v>
+        <v>559.2275828599861</v>
       </c>
       <c r="F33" t="n">
-        <v>289.2046403383179</v>
+        <v>538.3828936298074</v>
       </c>
       <c r="G33" t="n">
-        <v>283.1943982690126</v>
+        <v>210.1504293382799</v>
       </c>
       <c r="H33" t="n">
-        <v>244.2662750570162</v>
+        <v>52.40000000000117</v>
       </c>
       <c r="I33" t="n">
-        <v>52.40000000000321</v>
+        <v>52.40000000000117</v>
       </c>
       <c r="J33" t="n">
-        <v>250.1913459300192</v>
+        <v>250.1913459300171</v>
       </c>
       <c r="K33" t="n">
-        <v>565.5796394772328</v>
+        <v>565.5796394772308</v>
       </c>
       <c r="L33" t="n">
-        <v>1006.615493996961</v>
+        <v>1006.615493996959</v>
       </c>
       <c r="M33" t="n">
-        <v>1290.71088573982</v>
+        <v>1290.710885739818</v>
       </c>
       <c r="N33" t="n">
-        <v>1627.246884215313</v>
+        <v>1627.246884215311</v>
       </c>
       <c r="O33" t="n">
-        <v>2052.228604861296</v>
+        <v>2052.228604861294</v>
       </c>
       <c r="P33" t="n">
-        <v>2313.990605368539</v>
+        <v>2313.990605368537</v>
       </c>
       <c r="Q33" t="n">
-        <v>2313.990605368539</v>
+        <v>2240.946636437806</v>
       </c>
       <c r="R33" t="n">
-        <v>2132.917892265888</v>
+        <v>2059.873923335155</v>
       </c>
       <c r="S33" t="n">
-        <v>1998.674143492791</v>
+        <v>1925.630174562058</v>
       </c>
       <c r="T33" t="n">
-        <v>1914.658037974814</v>
+        <v>1841.614069044082</v>
       </c>
       <c r="U33" t="n">
-        <v>1832.679830098125</v>
+        <v>1759.635861167392</v>
       </c>
       <c r="V33" t="n">
-        <v>1736.204408692549</v>
+        <v>1340.938217539594</v>
       </c>
       <c r="W33" t="n">
-        <v>1621.686082521005</v>
+        <v>904.1976691458276</v>
       </c>
       <c r="X33" t="n">
-        <v>1197.582305303442</v>
+        <v>802.3161141504867</v>
       </c>
       <c r="Y33" t="n">
-        <v>1116.378878266942</v>
+        <v>721.1126871139874</v>
       </c>
     </row>
     <row r="34">
@@ -6825,76 +6825,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>673.4417775581377</v>
+        <v>673.4417775581356</v>
       </c>
       <c r="C34" t="n">
-        <v>719.2537833765734</v>
+        <v>719.2537833765714</v>
       </c>
       <c r="D34" t="n">
-        <v>752.3829275015735</v>
+        <v>752.3829275015714</v>
       </c>
       <c r="E34" t="n">
-        <v>790.0218317129865</v>
+        <v>790.0218317129844</v>
       </c>
       <c r="F34" t="n">
-        <v>834.192804304922</v>
+        <v>834.1928043049199</v>
       </c>
       <c r="G34" t="n">
-        <v>908.0645554377089</v>
+        <v>908.0645554377069</v>
       </c>
       <c r="H34" t="n">
-        <v>1003.216333056123</v>
+        <v>1003.216333056121</v>
       </c>
       <c r="I34" t="n">
-        <v>1163.862419205321</v>
+        <v>1163.862419205318</v>
       </c>
       <c r="J34" t="n">
-        <v>1491.077756743031</v>
+        <v>1491.077756743016</v>
       </c>
       <c r="K34" t="n">
-        <v>1597.372803794653</v>
+        <v>1597.372803794638</v>
       </c>
       <c r="L34" t="n">
-        <v>1591.155096928872</v>
+        <v>1591.155096928857</v>
       </c>
       <c r="M34" t="n">
-        <v>1492.275360291092</v>
+        <v>1492.275360291077</v>
       </c>
       <c r="N34" t="n">
-        <v>1339.839881046635</v>
+        <v>1339.839881046619</v>
       </c>
       <c r="O34" t="n">
-        <v>1109.635154952581</v>
+        <v>1109.635154952565</v>
       </c>
       <c r="P34" t="n">
-        <v>818.3161660963971</v>
+        <v>818.3161660963816</v>
       </c>
       <c r="Q34" t="n">
-        <v>463.3441798079143</v>
+        <v>463.3441798078988</v>
       </c>
       <c r="R34" t="n">
-        <v>81.68251716757283</v>
+        <v>84.56167017509942</v>
       </c>
       <c r="S34" t="n">
-        <v>52.40000000000321</v>
+        <v>52.40000000000117</v>
       </c>
       <c r="T34" t="n">
-        <v>163.0851070276605</v>
+        <v>163.0851070276585</v>
       </c>
       <c r="U34" t="n">
-        <v>329.4820370429964</v>
+        <v>329.4820370429943</v>
       </c>
       <c r="V34" t="n">
-        <v>448.1134299289423</v>
+        <v>448.1134299289403</v>
       </c>
       <c r="W34" t="n">
-        <v>539.8143481886198</v>
+        <v>539.8143481886177</v>
       </c>
       <c r="X34" t="n">
-        <v>610.6551392128133</v>
+        <v>610.6551392128113</v>
       </c>
       <c r="Y34" t="n">
-        <v>641.8744398918456</v>
+        <v>641.8744398918435</v>
       </c>
     </row>
     <row r="35">
@@ -6904,76 +6904,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>117.140856262951</v>
+        <v>117.140856262949</v>
       </c>
       <c r="C35" t="n">
-        <v>64.13623177507836</v>
+        <v>64.13623177507631</v>
       </c>
       <c r="D35" t="n">
-        <v>50.6623370883614</v>
+        <v>50.66233708835936</v>
       </c>
       <c r="E35" t="n">
-        <v>43.22467081879711</v>
+        <v>43.22467081879507</v>
       </c>
       <c r="F35" t="n">
-        <v>35.2553488915124</v>
+        <v>35.25534889151037</v>
       </c>
       <c r="G35" t="n">
-        <v>29.92000000000321</v>
+        <v>29.92000000000117</v>
       </c>
       <c r="H35" t="n">
-        <v>29.92000000000321</v>
+        <v>29.92000000000117</v>
       </c>
       <c r="I35" t="n">
-        <v>29.92000000000321</v>
+        <v>29.92000000000117</v>
       </c>
       <c r="J35" t="n">
-        <v>119.1959849731427</v>
+        <v>119.1959849731407</v>
       </c>
       <c r="K35" t="n">
-        <v>304.9927226113336</v>
+        <v>304.9927226113316</v>
       </c>
       <c r="L35" t="n">
-        <v>535.4900049228914</v>
+        <v>535.4900049228894</v>
       </c>
       <c r="M35" t="n">
-        <v>739.4315875549098</v>
+        <v>739.4315875548458</v>
       </c>
       <c r="N35" t="n">
-        <v>1109.691587554968</v>
+        <v>1109.691587554866</v>
       </c>
       <c r="O35" t="n">
-        <v>1286.24475964144</v>
+        <v>1286.244759641338</v>
       </c>
       <c r="P35" t="n">
-        <v>1496.000000000161</v>
+        <v>1496.000000000059</v>
       </c>
       <c r="Q35" t="n">
-        <v>1496.000000000161</v>
+        <v>1496.000000000059</v>
       </c>
       <c r="R35" t="n">
-        <v>1496.000000000161</v>
+        <v>1496.000000000059</v>
       </c>
       <c r="S35" t="n">
-        <v>1431.123215102631</v>
+        <v>1434.457487638387</v>
       </c>
       <c r="T35" t="n">
-        <v>1246.055417711716</v>
+        <v>1249.389690247471</v>
       </c>
       <c r="U35" t="n">
-        <v>991.4056536734765</v>
+        <v>994.7399262092318</v>
       </c>
       <c r="V35" t="n">
-        <v>756.202598959513</v>
+        <v>759.5368714952683</v>
       </c>
       <c r="W35" t="n">
-        <v>512.3910070595659</v>
+        <v>515.7252795953214</v>
       </c>
       <c r="X35" t="n">
-        <v>318.4709023623257</v>
+        <v>318.4709023623236</v>
       </c>
       <c r="Y35" t="n">
-        <v>202.9987481372687</v>
+        <v>202.9987481372667</v>
       </c>
     </row>
     <row r="36">
@@ -6983,76 +6983,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>567.9197065943017</v>
+        <v>29.92000000000117</v>
       </c>
       <c r="C36" t="n">
-        <v>567.9197065943017</v>
+        <v>29.92000000000117</v>
       </c>
       <c r="D36" t="n">
-        <v>567.9197065943017</v>
+        <v>29.92000000000117</v>
       </c>
       <c r="E36" t="n">
-        <v>221.7862750570162</v>
+        <v>29.92000000000117</v>
       </c>
       <c r="F36" t="n">
-        <v>221.7862750570162</v>
+        <v>29.92000000000117</v>
       </c>
       <c r="G36" t="n">
-        <v>221.7862750570162</v>
+        <v>29.92000000000117</v>
       </c>
       <c r="H36" t="n">
-        <v>221.7862750570162</v>
+        <v>29.92000000000117</v>
       </c>
       <c r="I36" t="n">
-        <v>29.92000000000321</v>
+        <v>29.92000000000117</v>
       </c>
       <c r="J36" t="n">
-        <v>195.2641644697357</v>
+        <v>227.7113459300171</v>
       </c>
       <c r="K36" t="n">
-        <v>510.6524580169493</v>
+        <v>543.0996394772308</v>
       </c>
       <c r="L36" t="n">
-        <v>567.4798694414776</v>
+        <v>904.0158679168685</v>
       </c>
       <c r="M36" t="n">
-        <v>851.5752611843368</v>
+        <v>1188.111259659728</v>
       </c>
       <c r="N36" t="n">
-        <v>1188.11125965983</v>
+        <v>1188.111259659728</v>
       </c>
       <c r="O36" t="n">
-        <v>1234.237999492918</v>
+        <v>1234.237999492816</v>
       </c>
       <c r="P36" t="n">
-        <v>1496.000000000161</v>
+        <v>1496.000000000059</v>
       </c>
       <c r="Q36" t="n">
-        <v>1422.95603106943</v>
+        <v>1496.000000000059</v>
       </c>
       <c r="R36" t="n">
-        <v>1320.671196754658</v>
+        <v>1393.715165685286</v>
       </c>
       <c r="S36" t="n">
-        <v>1265.21532676944</v>
+        <v>1227.683334261954</v>
       </c>
       <c r="T36" t="n">
-        <v>1259.987100039342</v>
+        <v>849.9055564841559</v>
       </c>
       <c r="U36" t="n">
-        <v>1256.796770950531</v>
+        <v>846.7152273953452</v>
       </c>
       <c r="V36" t="n">
-        <v>1239.109228332834</v>
+        <v>468.9374496175471</v>
       </c>
       <c r="W36" t="n">
-        <v>1203.378780949169</v>
+        <v>433.207002233882</v>
       </c>
       <c r="X36" t="n">
-        <v>945.6974843721384</v>
+        <v>410.1133260264198</v>
       </c>
       <c r="Y36" t="n">
-        <v>567.9197065943017</v>
+        <v>407.6977777777992</v>
       </c>
     </row>
     <row r="37">
@@ -7062,76 +7062,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>817.3938833471346</v>
+        <v>441.361838202727</v>
       </c>
       <c r="C37" t="n">
-        <v>817.3938833471346</v>
+        <v>441.361838202727</v>
       </c>
       <c r="D37" t="n">
-        <v>817.3938833471346</v>
+        <v>441.361838202727</v>
       </c>
       <c r="E37" t="n">
-        <v>817.3938833471346</v>
+        <v>441.361838202727</v>
       </c>
       <c r="F37" t="n">
-        <v>817.3938833471346</v>
+        <v>562.7528107946624</v>
       </c>
       <c r="G37" t="n">
-        <v>817.3938833471346</v>
+        <v>562.7528107946624</v>
       </c>
       <c r="H37" t="n">
-        <v>817.3938833471346</v>
+        <v>562.7528107946624</v>
       </c>
       <c r="I37" t="n">
-        <v>1055.259969496332</v>
+        <v>800.6188969438601</v>
       </c>
       <c r="J37" t="n">
-        <v>1066.66530703403</v>
+        <v>812.0242344815573</v>
       </c>
       <c r="K37" t="n">
-        <v>1066.66530703403</v>
+        <v>995.5392815331797</v>
       </c>
       <c r="L37" t="n">
-        <v>1066.66530703403</v>
+        <v>1066.665307034028</v>
       </c>
       <c r="M37" t="n">
-        <v>1046.573449184128</v>
+        <v>1046.573449184126</v>
       </c>
       <c r="N37" t="n">
-        <v>972.9258487275498</v>
+        <v>972.9258487275478</v>
       </c>
       <c r="O37" t="n">
-        <v>821.5090014213747</v>
+        <v>821.5090014213727</v>
       </c>
       <c r="P37" t="n">
-        <v>608.9778913530698</v>
+        <v>608.9778913530678</v>
       </c>
       <c r="Q37" t="n">
-        <v>332.7937838524658</v>
+        <v>332.7937838524638</v>
       </c>
       <c r="R37" t="n">
-        <v>29.92000000000321</v>
+        <v>29.92000000000117</v>
       </c>
       <c r="S37" t="n">
-        <v>75.61834706138944</v>
+        <v>29.92000000000117</v>
       </c>
       <c r="T37" t="n">
-        <v>263.5234540890468</v>
+        <v>217.8251070276585</v>
       </c>
       <c r="U37" t="n">
-        <v>344.182271522479</v>
+        <v>217.8251070276585</v>
       </c>
       <c r="V37" t="n">
-        <v>540.033664408425</v>
+        <v>413.6764999136045</v>
       </c>
       <c r="W37" t="n">
-        <v>708.9545826681024</v>
+        <v>441.361838202727</v>
       </c>
       <c r="X37" t="n">
-        <v>708.9545826681024</v>
+        <v>441.361838202727</v>
       </c>
       <c r="Y37" t="n">
-        <v>817.3938833471346</v>
+        <v>441.361838202727</v>
       </c>
     </row>
     <row r="38">
@@ -7141,76 +7141,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>117.140856262951</v>
+        <v>117.140856262949</v>
       </c>
       <c r="C38" t="n">
-        <v>64.13623177507833</v>
+        <v>64.13623177507631</v>
       </c>
       <c r="D38" t="n">
-        <v>50.66233708836137</v>
+        <v>50.66233708835936</v>
       </c>
       <c r="E38" t="n">
-        <v>43.22467081879708</v>
+        <v>43.22467081879507</v>
       </c>
       <c r="F38" t="n">
-        <v>35.25534889151238</v>
+        <v>35.25534889151037</v>
       </c>
       <c r="G38" t="n">
-        <v>29.92000000000321</v>
+        <v>29.92000000000117</v>
       </c>
       <c r="H38" t="n">
-        <v>29.92000000000321</v>
+        <v>29.92000000000117</v>
       </c>
       <c r="I38" t="n">
-        <v>29.92000000000321</v>
+        <v>29.92000000000117</v>
       </c>
       <c r="J38" t="n">
-        <v>119.1959849731427</v>
+        <v>119.1959849731407</v>
       </c>
       <c r="K38" t="n">
-        <v>304.9927226113336</v>
+        <v>304.9927226113316</v>
       </c>
       <c r="L38" t="n">
-        <v>535.4900049228914</v>
+        <v>535.4900049228894</v>
       </c>
       <c r="M38" t="n">
-        <v>535.4900049228914</v>
+        <v>578.926827913496</v>
       </c>
       <c r="N38" t="n">
-        <v>578.9268279135042</v>
+        <v>578.926827913496</v>
       </c>
       <c r="O38" t="n">
-        <v>755.4799999999768</v>
+        <v>755.4799999999686</v>
       </c>
       <c r="P38" t="n">
-        <v>1125.740000000069</v>
+        <v>1125.740000000014</v>
       </c>
       <c r="Q38" t="n">
-        <v>1496.000000000161</v>
+        <v>1496.000000000059</v>
       </c>
       <c r="R38" t="n">
-        <v>1496.000000000161</v>
+        <v>1496.000000000059</v>
       </c>
       <c r="S38" t="n">
-        <v>1434.457487638389</v>
+        <v>1431.123215102529</v>
       </c>
       <c r="T38" t="n">
-        <v>1249.389690247473</v>
+        <v>1249.389690247471</v>
       </c>
       <c r="U38" t="n">
-        <v>994.7399262092339</v>
+        <v>994.7399262092318</v>
       </c>
       <c r="V38" t="n">
-        <v>759.5368714952704</v>
+        <v>759.5368714952683</v>
       </c>
       <c r="W38" t="n">
-        <v>515.7252795953233</v>
+        <v>515.7252795953214</v>
       </c>
       <c r="X38" t="n">
-        <v>318.4709023623256</v>
+        <v>318.4709023623236</v>
       </c>
       <c r="Y38" t="n">
-        <v>202.9987481372686</v>
+        <v>202.9987481372667</v>
       </c>
     </row>
     <row r="39">
@@ -7220,76 +7220,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>573.2384840445947</v>
+        <v>805.3200054452585</v>
       </c>
       <c r="C39" t="n">
-        <v>573.2384840445947</v>
+        <v>805.3200054452585</v>
       </c>
       <c r="D39" t="n">
-        <v>221.7862750570162</v>
+        <v>805.3200054452585</v>
       </c>
       <c r="E39" t="n">
-        <v>221.7862750570162</v>
+        <v>805.3200054452585</v>
       </c>
       <c r="F39" t="n">
-        <v>221.7862750570162</v>
+        <v>805.3200054452585</v>
       </c>
       <c r="G39" t="n">
-        <v>221.7862750570162</v>
+        <v>549.6086806388766</v>
       </c>
       <c r="H39" t="n">
-        <v>221.7862750570162</v>
+        <v>221.7862750570142</v>
       </c>
       <c r="I39" t="n">
-        <v>29.92000000000321</v>
+        <v>29.92000000000117</v>
       </c>
       <c r="J39" t="n">
-        <v>227.7113459300191</v>
+        <v>227.7113459300171</v>
       </c>
       <c r="K39" t="n">
-        <v>543.0996394772328</v>
+        <v>250.1782010228474</v>
       </c>
       <c r="L39" t="n">
-        <v>599.9270509017612</v>
+        <v>620.4382010228924</v>
       </c>
       <c r="M39" t="n">
-        <v>884.0224426446205</v>
+        <v>904.5335927657516</v>
       </c>
       <c r="N39" t="n">
-        <v>1188.11125965983</v>
+        <v>1188.111259659728</v>
       </c>
       <c r="O39" t="n">
-        <v>1234.237999492918</v>
+        <v>1234.237999492816</v>
       </c>
       <c r="P39" t="n">
-        <v>1496.000000000161</v>
+        <v>1496.000000000059</v>
       </c>
       <c r="Q39" t="n">
-        <v>1422.95603106943</v>
+        <v>1422.956031069328</v>
       </c>
       <c r="R39" t="n">
-        <v>1058.087454700373</v>
+        <v>1320.671196754556</v>
       </c>
       <c r="S39" t="n">
-        <v>1002.631584715155</v>
+        <v>1265.215326769338</v>
       </c>
       <c r="T39" t="n">
-        <v>997.4033579850567</v>
+        <v>887.4375489915142</v>
       </c>
       <c r="U39" t="n">
-        <v>994.213028896246</v>
+        <v>884.2472199027035</v>
       </c>
       <c r="V39" t="n">
-        <v>976.5254862785489</v>
+        <v>866.5596772850064</v>
       </c>
       <c r="W39" t="n">
-        <v>598.7477085006774</v>
+        <v>830.8292299013413</v>
       </c>
       <c r="X39" t="n">
-        <v>575.6540322932152</v>
+        <v>807.7355536938791</v>
       </c>
       <c r="Y39" t="n">
-        <v>573.2384840445947</v>
+        <v>805.3200054452585</v>
       </c>
     </row>
     <row r="40">
@@ -7299,76 +7299,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>630.9031382589309</v>
+        <v>694.3618775286968</v>
       </c>
       <c r="C40" t="n">
-        <v>753.9351440773667</v>
+        <v>817.3938833471326</v>
       </c>
       <c r="D40" t="n">
-        <v>753.9351440773667</v>
+        <v>817.3938833471326</v>
       </c>
       <c r="E40" t="n">
-        <v>868.7940482887797</v>
+        <v>817.3938833471326</v>
       </c>
       <c r="F40" t="n">
-        <v>904.1682183635453</v>
+        <v>817.3938833471326</v>
       </c>
       <c r="G40" t="n">
-        <v>1055.259969496332</v>
+        <v>817.3938833471326</v>
       </c>
       <c r="H40" t="n">
-        <v>1055.259969496332</v>
+        <v>817.3938833471326</v>
       </c>
       <c r="I40" t="n">
-        <v>1055.259969496332</v>
+        <v>1055.25996949633</v>
       </c>
       <c r="J40" t="n">
-        <v>1066.665307034029</v>
+        <v>1066.665307034028</v>
       </c>
       <c r="K40" t="n">
-        <v>1066.665307034029</v>
+        <v>1066.665307034028</v>
       </c>
       <c r="L40" t="n">
-        <v>1066.665307034029</v>
+        <v>1066.665307034028</v>
       </c>
       <c r="M40" t="n">
-        <v>1046.573449184128</v>
+        <v>1046.573449184126</v>
       </c>
       <c r="N40" t="n">
-        <v>972.9258487275496</v>
+        <v>972.9258487275478</v>
       </c>
       <c r="O40" t="n">
-        <v>821.5090014213745</v>
+        <v>821.5090014213727</v>
       </c>
       <c r="P40" t="n">
-        <v>608.9778913530697</v>
+        <v>608.9778913530678</v>
       </c>
       <c r="Q40" t="n">
-        <v>332.7937838524658</v>
+        <v>332.7937838524638</v>
       </c>
       <c r="R40" t="n">
-        <v>29.92000000000321</v>
+        <v>29.92000000000117</v>
       </c>
       <c r="S40" t="n">
-        <v>29.92000000000321</v>
+        <v>29.92000000000117</v>
       </c>
       <c r="T40" t="n">
-        <v>217.8251070276605</v>
+        <v>217.8251070276585</v>
       </c>
       <c r="U40" t="n">
-        <v>217.8251070276605</v>
+        <v>217.8251070276585</v>
       </c>
       <c r="V40" t="n">
-        <v>413.6764999136064</v>
+        <v>217.8251070276585</v>
       </c>
       <c r="W40" t="n">
-        <v>413.6764999136064</v>
+        <v>386.7460252873359</v>
       </c>
       <c r="X40" t="n">
-        <v>413.6764999136064</v>
+        <v>534.8068163115295</v>
       </c>
       <c r="Y40" t="n">
-        <v>522.1158005926387</v>
+        <v>585.5745398624047</v>
       </c>
     </row>
     <row r="41">
@@ -7378,76 +7378,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>630.2826001800496</v>
+        <v>743.3024271578373</v>
       </c>
       <c r="C41" t="n">
-        <v>472.2274706416719</v>
+        <v>585.2472976194596</v>
       </c>
       <c r="D41" t="n">
-        <v>353.7030709044499</v>
+        <v>466.7228978822376</v>
       </c>
       <c r="E41" t="n">
-        <v>241.2148995843805</v>
+        <v>354.2347265621682</v>
       </c>
       <c r="F41" t="n">
-        <v>241.2148995843805</v>
+        <v>241.2148995843785</v>
       </c>
       <c r="G41" t="n">
-        <v>130.8290456423663</v>
+        <v>130.8290456423643</v>
       </c>
       <c r="H41" t="n">
-        <v>29.92000000000321</v>
+        <v>29.92000000000117</v>
       </c>
       <c r="I41" t="n">
-        <v>29.92000000000321</v>
+        <v>29.92000000000117</v>
       </c>
       <c r="J41" t="n">
-        <v>119.1959849731427</v>
+        <v>119.1959849731407</v>
       </c>
       <c r="K41" t="n">
-        <v>304.9927226113336</v>
+        <v>489.4559849731552</v>
       </c>
       <c r="L41" t="n">
-        <v>535.4900049228914</v>
+        <v>719.9532672847129</v>
       </c>
       <c r="M41" t="n">
-        <v>535.4900049228914</v>
+        <v>719.953267284713</v>
       </c>
       <c r="N41" t="n">
-        <v>905.7500049230284</v>
+        <v>739.4315875547936</v>
       </c>
       <c r="O41" t="n">
-        <v>1082.303177009501</v>
+        <v>915.9847596412662</v>
       </c>
       <c r="P41" t="n">
-        <v>1292.058417368221</v>
+        <v>1125.739999999987</v>
       </c>
       <c r="Q41" t="n">
-        <v>1496.000000000161</v>
+        <v>1496.000000000059</v>
       </c>
       <c r="R41" t="n">
-        <v>1496.000000000161</v>
+        <v>1496.000000000059</v>
       </c>
       <c r="S41" t="n">
-        <v>1326.072710052126</v>
+        <v>1496.000000000059</v>
       </c>
       <c r="T41" t="n">
-        <v>1035.954407610706</v>
+        <v>1496.000000000059</v>
       </c>
       <c r="U41" t="n">
-        <v>979.1446971305018</v>
+        <v>1496.000000000059</v>
       </c>
       <c r="V41" t="n">
-        <v>979.1446971305018</v>
+        <v>1496.000000000059</v>
       </c>
       <c r="W41" t="n">
-        <v>630.2826001800496</v>
+        <v>1154.733483358222</v>
       </c>
       <c r="X41" t="n">
-        <v>630.2826001800496</v>
+        <v>1154.733483358222</v>
       </c>
       <c r="Y41" t="n">
-        <v>630.2826001800496</v>
+        <v>934.2108240826601</v>
       </c>
     </row>
     <row r="42">
@@ -7457,76 +7457,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>315.6172324016875</v>
+        <v>318.0281146698491</v>
       </c>
       <c r="C42" t="n">
-        <v>246.8294420526781</v>
+        <v>249.2403243208397</v>
       </c>
       <c r="D42" t="n">
-        <v>191.3368290246957</v>
+        <v>193.7477112928572</v>
       </c>
       <c r="E42" t="n">
-        <v>141.1629934470062</v>
+        <v>143.5738757151677</v>
       </c>
       <c r="F42" t="n">
-        <v>94.05567795420123</v>
+        <v>96.46656022236282</v>
       </c>
       <c r="G42" t="n">
-        <v>61.78280962226964</v>
+        <v>64.19369189043124</v>
       </c>
       <c r="H42" t="n">
-        <v>29.92000000000321</v>
+        <v>29.92000000000117</v>
       </c>
       <c r="I42" t="n">
-        <v>29.92000000000321</v>
+        <v>29.92000000000117</v>
       </c>
       <c r="J42" t="n">
-        <v>227.7113459300191</v>
+        <v>29.92000000000117</v>
       </c>
       <c r="K42" t="n">
-        <v>543.0996394772328</v>
+        <v>52.3868550928314</v>
       </c>
       <c r="L42" t="n">
-        <v>904.0158679169704</v>
+        <v>422.6468550929035</v>
       </c>
       <c r="M42" t="n">
-        <v>1188.11125965983</v>
+        <v>706.7422468357627</v>
       </c>
       <c r="N42" t="n">
-        <v>1188.11125965983</v>
+        <v>1043.278245311255</v>
       </c>
       <c r="O42" t="n">
-        <v>1234.237999492918</v>
+        <v>1234.237999492816</v>
       </c>
       <c r="P42" t="n">
-        <v>1496.000000000161</v>
+        <v>1496.000000000059</v>
       </c>
       <c r="Q42" t="n">
-        <v>1496.000000000161</v>
+        <v>1496.000000000059</v>
       </c>
       <c r="R42" t="n">
-        <v>1288.664660634883</v>
+        <v>1288.664660634781</v>
       </c>
       <c r="S42" t="n">
-        <v>1128.15828559916</v>
+        <v>1128.158285599058</v>
       </c>
       <c r="T42" t="n">
-        <v>1017.879553818557</v>
+        <v>1017.879553818455</v>
       </c>
       <c r="U42" t="n">
-        <v>909.6387196792411</v>
+        <v>909.6387196791393</v>
       </c>
       <c r="V42" t="n">
-        <v>786.900672011039</v>
+        <v>786.9006720109371</v>
       </c>
       <c r="W42" t="n">
-        <v>643.7088373086053</v>
+        <v>646.1197195767669</v>
       </c>
       <c r="X42" t="n">
-        <v>515.5646560506381</v>
+        <v>517.9755383187996</v>
       </c>
       <c r="Y42" t="n">
-        <v>408.0986027515124</v>
+        <v>410.509485019674</v>
       </c>
     </row>
     <row r="43">
@@ -7536,76 +7536,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>470.7817775581376</v>
+        <v>470.7817775581356</v>
       </c>
       <c r="C43" t="n">
-        <v>490.8537833765734</v>
+        <v>490.8537833765714</v>
       </c>
       <c r="D43" t="n">
-        <v>498.2429275015735</v>
+        <v>498.2429275015714</v>
       </c>
       <c r="E43" t="n">
-        <v>510.1418317129865</v>
+        <v>510.1418317129845</v>
       </c>
       <c r="F43" t="n">
-        <v>528.572804304922</v>
+        <v>528.5728043049199</v>
       </c>
       <c r="G43" t="n">
-        <v>576.7045554377089</v>
+        <v>576.7045554377069</v>
       </c>
       <c r="H43" t="n">
-        <v>646.1163330561228</v>
+        <v>646.1163330561208</v>
       </c>
       <c r="I43" t="n">
-        <v>781.0224192053205</v>
+        <v>781.0224192053184</v>
       </c>
       <c r="J43" t="n">
-        <v>1082.497756743018</v>
+        <v>1082.497756743016</v>
       </c>
       <c r="K43" t="n">
-        <v>1163.05280379464</v>
+        <v>1163.052803794638</v>
       </c>
       <c r="L43" t="n">
-        <v>1163.05280379464</v>
+        <v>1130.572470666231</v>
       </c>
       <c r="M43" t="n">
-        <v>1163.05280379464</v>
+        <v>1005.430107765824</v>
       </c>
       <c r="N43" t="n">
-        <v>1163.05280379464</v>
+        <v>826.7320022587407</v>
       </c>
       <c r="O43" t="n">
-        <v>906.5854514379603</v>
+        <v>783.7036893348651</v>
       </c>
       <c r="P43" t="n">
-        <v>589.0038363191504</v>
+        <v>466.1220742160552</v>
       </c>
       <c r="Q43" t="n">
-        <v>211.2260585412329</v>
+        <v>466.1220742160552</v>
       </c>
       <c r="R43" t="n">
-        <v>29.92000000000321</v>
+        <v>88.34429643772569</v>
       </c>
       <c r="S43" t="n">
-        <v>29.92000000000321</v>
+        <v>29.92000000000117</v>
       </c>
       <c r="T43" t="n">
-        <v>114.8651070276605</v>
+        <v>114.8651070276585</v>
       </c>
       <c r="U43" t="n">
-        <v>255.5220370429963</v>
+        <v>255.5220370429943</v>
       </c>
       <c r="V43" t="n">
-        <v>348.4134299289423</v>
+        <v>348.4134299289403</v>
       </c>
       <c r="W43" t="n">
-        <v>414.3743481886197</v>
+        <v>414.3743481886177</v>
       </c>
       <c r="X43" t="n">
-        <v>459.4751392128132</v>
+        <v>459.4751392128112</v>
       </c>
       <c r="Y43" t="n">
-        <v>464.9544398918455</v>
+        <v>464.9544398918434</v>
       </c>
     </row>
     <row r="44">
@@ -7615,76 +7615,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>743.3024271578394</v>
+        <v>504.7924509213126</v>
       </c>
       <c r="C44" t="n">
-        <v>585.2472976194616</v>
+        <v>466.7228978822376</v>
       </c>
       <c r="D44" t="n">
-        <v>466.7228978822396</v>
+        <v>466.7228978822376</v>
       </c>
       <c r="E44" t="n">
-        <v>354.2347265621703</v>
+        <v>354.2347265621683</v>
       </c>
       <c r="F44" t="n">
-        <v>241.2148995843806</v>
+        <v>241.2148995843785</v>
       </c>
       <c r="G44" t="n">
-        <v>130.8290456423663</v>
+        <v>130.8290456423643</v>
       </c>
       <c r="H44" t="n">
-        <v>29.92000000000321</v>
+        <v>29.92000000000117</v>
       </c>
       <c r="I44" t="n">
-        <v>29.92000000000321</v>
+        <v>29.92000000000117</v>
       </c>
       <c r="J44" t="n">
-        <v>119.1959849731427</v>
+        <v>119.1959849731407</v>
       </c>
       <c r="K44" t="n">
-        <v>304.9927226113336</v>
+        <v>304.9927226113316</v>
       </c>
       <c r="L44" t="n">
-        <v>535.4900049228914</v>
+        <v>535.4900049228894</v>
       </c>
       <c r="M44" t="n">
-        <v>905.7500049231544</v>
+        <v>535.4900049228894</v>
       </c>
       <c r="N44" t="n">
-        <v>1109.691587554968</v>
+        <v>578.9268279132691</v>
       </c>
       <c r="O44" t="n">
-        <v>1286.24475964144</v>
+        <v>755.4799999997417</v>
       </c>
       <c r="P44" t="n">
-        <v>1496.000000000161</v>
+        <v>1125.7399999999</v>
       </c>
       <c r="Q44" t="n">
-        <v>1496.000000000161</v>
+        <v>1496.000000000059</v>
       </c>
       <c r="R44" t="n">
-        <v>1496.000000000161</v>
+        <v>1496.000000000059</v>
       </c>
       <c r="S44" t="n">
-        <v>1496.000000000161</v>
+        <v>1326.072710052024</v>
       </c>
       <c r="T44" t="n">
-        <v>1496.000000000161</v>
+        <v>1035.954407610604</v>
       </c>
       <c r="U44" t="n">
-        <v>1136.299730911416</v>
+        <v>1035.954407610604</v>
       </c>
       <c r="V44" t="n">
-        <v>1136.299730911416</v>
+        <v>695.7008478461354</v>
       </c>
       <c r="W44" t="n">
-        <v>1136.299730911416</v>
+        <v>695.7008478461354</v>
       </c>
       <c r="X44" t="n">
-        <v>1136.299730911416</v>
+        <v>695.7008478461354</v>
       </c>
       <c r="Y44" t="n">
-        <v>934.2108240826622</v>
+        <v>695.7008478461354</v>
       </c>
     </row>
     <row r="45">
@@ -7694,76 +7694,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>315.6172324016875</v>
+        <v>318.0281146698492</v>
       </c>
       <c r="C45" t="n">
-        <v>246.8294420526781</v>
+        <v>249.2403243208398</v>
       </c>
       <c r="D45" t="n">
-        <v>191.3368290246957</v>
+        <v>193.7477112928574</v>
       </c>
       <c r="E45" t="n">
-        <v>141.1629934470062</v>
+        <v>143.5738757151678</v>
       </c>
       <c r="F45" t="n">
-        <v>94.05567795420123</v>
+        <v>96.46656022236293</v>
       </c>
       <c r="G45" t="n">
-        <v>61.78280962226965</v>
+        <v>64.19369189043135</v>
       </c>
       <c r="H45" t="n">
-        <v>29.92000000000321</v>
+        <v>29.92000000000117</v>
       </c>
       <c r="I45" t="n">
-        <v>29.92000000000321</v>
+        <v>29.92000000000117</v>
       </c>
       <c r="J45" t="n">
-        <v>227.7113459300191</v>
+        <v>227.7113459300171</v>
       </c>
       <c r="K45" t="n">
-        <v>543.0996394772328</v>
+        <v>250.1782010228474</v>
       </c>
       <c r="L45" t="n">
-        <v>599.9270509017612</v>
+        <v>620.4382010230058</v>
       </c>
       <c r="M45" t="n">
-        <v>599.9270509017612</v>
+        <v>904.533592765865</v>
       </c>
       <c r="N45" t="n">
-        <v>936.4630493772539</v>
+        <v>1188.111259659728</v>
       </c>
       <c r="O45" t="n">
-        <v>1234.237999492918</v>
+        <v>1234.237999492816</v>
       </c>
       <c r="P45" t="n">
-        <v>1496.000000000161</v>
+        <v>1496.000000000059</v>
       </c>
       <c r="Q45" t="n">
-        <v>1493.589117731897</v>
+        <v>1496.000000000059</v>
       </c>
       <c r="R45" t="n">
-        <v>1286.25377836662</v>
+        <v>1288.664660634781</v>
       </c>
       <c r="S45" t="n">
-        <v>1125.747403330896</v>
+        <v>1128.158285599058</v>
       </c>
       <c r="T45" t="n">
-        <v>1015.468671550293</v>
+        <v>1017.879553818455</v>
       </c>
       <c r="U45" t="n">
-        <v>907.2278374109777</v>
+        <v>909.6387196791394</v>
       </c>
       <c r="V45" t="n">
-        <v>784.4897897427755</v>
+        <v>786.9006720109372</v>
       </c>
       <c r="W45" t="n">
-        <v>643.7088373086053</v>
+        <v>646.119719576767</v>
       </c>
       <c r="X45" t="n">
-        <v>515.5646560506381</v>
+        <v>517.9755383187997</v>
       </c>
       <c r="Y45" t="n">
-        <v>408.0986027515124</v>
+        <v>410.5094850196741</v>
       </c>
     </row>
     <row r="46">
@@ -7773,76 +7773,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>470.7817775581376</v>
+        <v>470.7817775581356</v>
       </c>
       <c r="C46" t="n">
-        <v>490.8537833765734</v>
+        <v>490.8537833765714</v>
       </c>
       <c r="D46" t="n">
-        <v>498.2429275015735</v>
+        <v>498.2429275015714</v>
       </c>
       <c r="E46" t="n">
-        <v>510.1418317129865</v>
+        <v>510.1418317129845</v>
       </c>
       <c r="F46" t="n">
-        <v>528.572804304922</v>
+        <v>528.5728043049199</v>
       </c>
       <c r="G46" t="n">
-        <v>576.7045554377089</v>
+        <v>576.7045554377069</v>
       </c>
       <c r="H46" t="n">
-        <v>646.1163330561228</v>
+        <v>646.1163330561208</v>
       </c>
       <c r="I46" t="n">
-        <v>781.0224192053205</v>
+        <v>781.0224192053184</v>
       </c>
       <c r="J46" t="n">
-        <v>1082.497756743018</v>
+        <v>1082.497756743016</v>
       </c>
       <c r="K46" t="n">
-        <v>1163.05280379464</v>
+        <v>1163.052803794638</v>
       </c>
       <c r="L46" t="n">
-        <v>1130.572470666233</v>
+        <v>1130.572470666231</v>
       </c>
       <c r="M46" t="n">
-        <v>1005.430107765827</v>
+        <v>1130.572470666231</v>
       </c>
       <c r="N46" t="n">
-        <v>826.7320022587429</v>
+        <v>1130.572470666231</v>
       </c>
       <c r="O46" t="n">
-        <v>570.2646499020627</v>
+        <v>874.1051183095506</v>
       </c>
       <c r="P46" t="n">
-        <v>252.6830347832528</v>
+        <v>556.5235031907407</v>
       </c>
       <c r="Q46" t="n">
-        <v>29.92000000000321</v>
+        <v>466.1220742162205</v>
       </c>
       <c r="R46" t="n">
-        <v>29.92000000000321</v>
+        <v>88.34429643772566</v>
       </c>
       <c r="S46" t="n">
-        <v>29.92000000000321</v>
+        <v>29.92000000000117</v>
       </c>
       <c r="T46" t="n">
-        <v>114.8651070276605</v>
+        <v>114.8651070276585</v>
       </c>
       <c r="U46" t="n">
-        <v>255.5220370429963</v>
+        <v>255.5220370429943</v>
       </c>
       <c r="V46" t="n">
-        <v>348.4134299289423</v>
+        <v>348.4134299289403</v>
       </c>
       <c r="W46" t="n">
-        <v>414.3743481886197</v>
+        <v>414.3743481886177</v>
       </c>
       <c r="X46" t="n">
-        <v>459.4751392128132</v>
+        <v>459.4751392128112</v>
       </c>
       <c r="Y46" t="n">
-        <v>464.9544398918455</v>
+        <v>464.9544398918434</v>
       </c>
     </row>
   </sheetData>
@@ -7964,10 +7964,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>374.2405037325275</v>
+        <v>0.2405037325275146</v>
       </c>
       <c r="K2" t="n">
-        <v>321.8400703517588</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -7976,16 +7976,16 @@
         <v>846.2608914614127</v>
       </c>
       <c r="N2" t="n">
-        <v>639.5838718235262</v>
+        <v>587.423942175285</v>
       </c>
       <c r="O2" t="n">
-        <v>1.159015302735668</v>
+        <v>375.1590153027356</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>128.5418702571336</v>
+        <v>502.5418702571336</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8204,19 +8204,19 @@
         <v>374.2405037325275</v>
       </c>
       <c r="K5" t="n">
-        <v>321.8400703517588</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>235.5012052109776</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>846.2608914614127</v>
       </c>
       <c r="N5" t="n">
-        <v>404.0826666125488</v>
+        <v>778.0826666125488</v>
       </c>
       <c r="O5" t="n">
-        <v>1.159015302735668</v>
+        <v>184.500290865472</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -8438,7 +8438,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>374.2405037325275</v>
+        <v>0.2405037325275146</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -8447,10 +8447,10 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>472.2608914614128</v>
+        <v>846.2608914614127</v>
       </c>
       <c r="N8" t="n">
-        <v>646.1026208280709</v>
+        <v>778.0826666125488</v>
       </c>
       <c r="O8" t="n">
         <v>1.159015302735668</v>
@@ -8459,7 +8459,7 @@
         <v>315.3213213472141</v>
       </c>
       <c r="Q8" t="n">
-        <v>502.5418702571336</v>
+        <v>370.5618244726559</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8684,10 +8684,10 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>940.1988562855336</v>
+        <v>892.5421829639406</v>
       </c>
       <c r="N11" t="n">
-        <v>218.9836043488682</v>
+        <v>868.9937721401875</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -8696,7 +8696,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>615.8520732695737</v>
+        <v>13.49857879984722</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8912,7 +8912,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -8921,19 +8921,19 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>285.1988562855334</v>
+        <v>892.5421829639406</v>
       </c>
       <c r="N14" t="n">
-        <v>868.993772140187</v>
+        <v>868.9937721401875</v>
       </c>
       <c r="O14" t="n">
-        <v>435.2945687948379</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>615.8520732695737</v>
+        <v>13.49857879984722</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9158,19 +9158,19 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>290.1886884942146</v>
+        <v>285.1988562855334</v>
       </c>
       <c r="N17" t="n">
-        <v>868.993772140187</v>
+        <v>868.9937721401875</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>476.6634625389171</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>615.8520732695737</v>
+        <v>144.1784429393371</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,19 +9386,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>382.6480632645645</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>940.1988562855336</v>
+        <v>290.1886884942141</v>
       </c>
       <c r="N20" t="n">
-        <v>868.993772140187</v>
+        <v>868.9937721401875</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>13.49857879984722</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9623,19 +9623,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>467.3265276381908</v>
+        <v>435.2945687948376</v>
       </c>
       <c r="L23" t="n">
-        <v>140.0167990402169</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>285.1988562855334</v>
+        <v>940.198856285534</v>
       </c>
       <c r="N23" t="n">
-        <v>868.993772140187</v>
+        <v>213.993772140187</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -9644,7 +9644,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>13.49857879984722</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9866,13 +9866,13 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>422.1744623115726</v>
       </c>
       <c r="M26" t="n">
-        <v>940.1988562855463</v>
+        <v>523.0142261827002</v>
       </c>
       <c r="N26" t="n">
-        <v>218.9836043490145</v>
+        <v>213.993772140187</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -10097,7 +10097,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -10106,19 +10106,19 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>285.1988562855334</v>
+        <v>940.1988562855363</v>
       </c>
       <c r="N29" t="n">
-        <v>868.9937721402075</v>
+        <v>213.993772140187</v>
       </c>
       <c r="O29" t="n">
-        <v>476.6634625389369</v>
+        <v>476.6634625389194</v>
       </c>
       <c r="P29" t="n">
-        <v>443.1260198396968</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>131.3571596858382</v>
+        <v>144.17844293935</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>940.1988562855663</v>
+        <v>940.1988562855372</v>
       </c>
       <c r="N32" t="n">
-        <v>821.3370988187207</v>
+        <v>821.3370988186491</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -10580,10 +10580,10 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>491.2004549037338</v>
+        <v>491.2004549036712</v>
       </c>
       <c r="N35" t="n">
-        <v>587.9937721402453</v>
+        <v>587.9937721402071</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -10650,19 +10650,19 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J36" t="n">
-        <v>194.6898111598254</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K36" t="n">
         <v>295.8802408630135</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>307.1604212273833</v>
       </c>
       <c r="M36" t="n">
         <v>471.6948204301074</v>
       </c>
       <c r="N36" t="n">
-        <v>485.4085271713503</v>
+        <v>145.473175175903</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -10817,19 +10817,19 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>285.1988562855334</v>
+        <v>329.0744350639239</v>
       </c>
       <c r="N38" t="n">
-        <v>257.8693509185837</v>
+        <v>213.993772140187</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>162.1260198397692</v>
+        <v>162.1260198397219</v>
       </c>
       <c r="Q38" t="n">
-        <v>387.4985787999401</v>
+        <v>387.4985787998928</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -10890,16 +10890,16 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K39" t="n">
-        <v>295.8802408630135</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>316.5985743187038</v>
       </c>
       <c r="M39" t="n">
         <v>471.6948204301074</v>
       </c>
       <c r="N39" t="n">
-        <v>452.6335964033869</v>
+        <v>431.915262947596</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -11048,7 +11048,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>186.3265276382056</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -11057,7 +11057,7 @@
         <v>285.1988562855334</v>
       </c>
       <c r="N41" t="n">
-        <v>587.9937721403253</v>
+        <v>233.6688431200664</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -11066,7 +11066,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>219.5001774179676</v>
+        <v>387.4985787999201</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11124,22 +11124,22 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J42" t="n">
-        <v>227.4647419277884</v>
+        <v>27.675503614641</v>
       </c>
       <c r="K42" t="n">
-        <v>295.8802408630135</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>307.1604212274841</v>
+        <v>316.5985743187311</v>
       </c>
       <c r="M42" t="n">
         <v>471.6948204301074</v>
       </c>
       <c r="N42" t="n">
-        <v>145.473175175903</v>
+        <v>485.4085271713503</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>146.2959740893658</v>
       </c>
       <c r="P42" t="n">
         <v>219.1507118405495</v>
@@ -11291,19 +11291,19 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>659.1988562857991</v>
+        <v>285.1988562855334</v>
       </c>
       <c r="N44" t="n">
-        <v>419.9953707581801</v>
+        <v>257.8693509183483</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>162.1260198398365</v>
       </c>
       <c r="Q44" t="n">
-        <v>13.49857879984722</v>
+        <v>387.4985788000074</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -11364,19 +11364,19 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K45" t="n">
-        <v>295.8802408630135</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>316.5985743188184</v>
       </c>
       <c r="M45" t="n">
-        <v>184.7297782656032</v>
+        <v>471.6948204301074</v>
       </c>
       <c r="N45" t="n">
-        <v>485.4085271713503</v>
+        <v>431.9152629474814</v>
       </c>
       <c r="O45" t="n">
-        <v>254.190111396541</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
         <v>219.1507118405495</v>
@@ -23232,64 +23232,64 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
         <v>0.6960849964949034</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -23411,13 +23411,13 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.850361477466352</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.850361477466578</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -23511,7 +23511,7 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6960849964951876</v>
+        <v>0.696084996495216</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
@@ -23657,7 +23657,7 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>2.850361477466521</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -23669,7 +23669,7 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.85036147746407</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -23906,7 +23906,7 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.850361477466322</v>
+        <v>2.85036147746407</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -23937,7 +23937,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>0.6960849964949034</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -23985,7 +23985,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6960849964951876</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -24134,7 +24134,7 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.850361477466265</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -24143,7 +24143,7 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.850361477464553</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -24186,7 +24186,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.696084996494875</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -24222,7 +24222,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6960849964155216</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -24362,7 +24362,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>2.850361477466308</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -24380,7 +24380,7 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.850361477466322</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -24423,7 +24423,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.6960849963391615</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -24474,7 +24474,7 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>0.69608499643806</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
@@ -24602,7 +24602,7 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.850361477466123</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -24617,7 +24617,7 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.850361477465931</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -24660,7 +24660,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.6960849964157012</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -24696,7 +24696,7 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>0.6960849964776514</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
@@ -24833,7 +24833,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>2.850361477466112</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -24848,7 +24848,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.850361477466606</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -24897,7 +24897,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.6960849963391615</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -24933,7 +24933,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>0.6960849964380316</v>
       </c>
       <c r="T32" t="n">
         <v>0</v>
@@ -25088,10 +25088,10 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.850361477466549</v>
       </c>
       <c r="S34" t="n">
-        <v>2.850361477453323</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -25170,7 +25170,7 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>3.300929810498623</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
@@ -25185,7 +25185,7 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>3.30092981039985</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
         <v>0</v>
@@ -25407,10 +25407,10 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>3.300929810399829</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>3.300929810498673</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -25593,7 +25593,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>188.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -25605,7 +25605,7 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>111.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -25644,25 +25644,25 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>168.2280170485541</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>287.2171194170061</v>
       </c>
       <c r="U41" t="n">
-        <v>299.8616530224549</v>
+        <v>356.1032663978569</v>
       </c>
       <c r="V41" t="n">
         <v>336.8510241668239</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>7.519624505529464</v>
       </c>
       <c r="X41" t="n">
         <v>299.2818334606677</v>
       </c>
       <c r="Y41" t="n">
-        <v>218.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -25781,28 +25781,28 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>32.15552979712345</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>123.8909392714024</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>176.9111244520127</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>211.3046490384764</v>
       </c>
       <c r="P43" t="n">
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.422266425459611</v>
+        <v>377.422266425598</v>
       </c>
       <c r="R43" t="n">
-        <v>224.3520480581205</v>
+        <v>29.84504601339177</v>
       </c>
       <c r="S43" t="n">
-        <v>57.84005347334727</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -25833,10 +25833,10 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>118.7857207343097</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>117.3391557398498</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -25881,16 +25881,16 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>168.2280170485541</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>287.2171194170061</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>356.1032663978569</v>
       </c>
       <c r="V44" t="n">
-        <v>336.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
         <v>345.3734759809475</v>
@@ -25899,7 +25899,7 @@
         <v>299.2818334606677</v>
       </c>
       <c r="Y44" t="n">
-        <v>18.24941492233989</v>
+        <v>218.3174326828064</v>
       </c>
     </row>
     <row r="45">
@@ -26021,10 +26021,10 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>123.8909392714024</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>176.9111244520127</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -26033,13 +26033,13 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>156.8868619901808</v>
+        <v>287.924851740823</v>
       </c>
       <c r="R46" t="n">
-        <v>403.845046013938</v>
+        <v>29.84504601322806</v>
       </c>
       <c r="S46" t="n">
-        <v>57.84005347334724</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8658811.325863691</v>
+        <v>8658811.325863685</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9729176.565661402</v>
+        <v>9729176.565661389</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10799541.8054591</v>
+        <v>10799541.80545909</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11869907.04525682</v>
+        <v>11869907.0452568</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12903363.08509292</v>
+        <v>12903363.08509289</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>13973610.22846467</v>
+        <v>13973610.22846463</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14933002.95285439</v>
+        <v>14933002.95285434</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15892395.67724411</v>
+        <v>15892395.67724405</v>
       </c>
     </row>
   </sheetData>
@@ -26284,34 +26284,34 @@
         <v>1133327.900962274</v>
       </c>
       <c r="G2" t="n">
-        <v>1133327.900962274</v>
+        <v>1133327.900962275</v>
       </c>
       <c r="H2" t="n">
         <v>1133327.900962274</v>
       </c>
       <c r="I2" t="n">
-        <v>1133327.90096228</v>
+        <v>1133327.900962275</v>
       </c>
       <c r="J2" t="n">
-        <v>1133327.900962285</v>
+        <v>1133327.900962278</v>
       </c>
       <c r="K2" t="n">
-        <v>1133327.90096228</v>
+        <v>1133327.900962276</v>
       </c>
       <c r="L2" t="n">
-        <v>1133327.900962285</v>
+        <v>1133327.900962279</v>
       </c>
       <c r="M2" t="n">
-        <v>1133202.857687718</v>
+        <v>1133202.857687711</v>
       </c>
       <c r="N2" t="n">
-        <v>1133202.857687717</v>
+        <v>1133202.857687711</v>
       </c>
       <c r="O2" t="n">
-        <v>1015827.590530285</v>
+        <v>1015827.590530277</v>
       </c>
       <c r="P2" t="n">
-        <v>1015827.590530284</v>
+        <v>1015827.590530277</v>
       </c>
     </row>
     <row r="3">
@@ -26345,7 +26345,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>386848.0000000141</v>
+        <v>386848.0000000051</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>602419.1762101186</v>
+        <v>602219.8615549037</v>
       </c>
       <c r="C4" t="n">
-        <v>600410.2540226299</v>
+        <v>600210.9393674152</v>
       </c>
       <c r="D4" t="n">
-        <v>598398.6066068059</v>
+        <v>598199.291951591</v>
       </c>
       <c r="E4" t="n">
-        <v>508463.6174685807</v>
+        <v>508269.4590428486</v>
       </c>
       <c r="F4" t="n">
-        <v>506794.9519687437</v>
+        <v>506600.7935430115</v>
       </c>
       <c r="G4" t="n">
-        <v>505123.9837731232</v>
+        <v>504929.8253473911</v>
       </c>
       <c r="H4" t="n">
-        <v>503450.6963689994</v>
+        <v>503256.5379432673</v>
       </c>
       <c r="I4" t="n">
-        <v>501775.073028504</v>
+        <v>501580.9146027682</v>
       </c>
       <c r="J4" t="n">
-        <v>500097.0968045256</v>
+        <v>499902.938378791</v>
       </c>
       <c r="K4" t="n">
-        <v>498416.750526552</v>
+        <v>498222.5921008182</v>
       </c>
       <c r="L4" t="n">
-        <v>496734.0167963795</v>
+        <v>496539.8583706446</v>
       </c>
       <c r="M4" t="n">
-        <v>522490.4615842171</v>
+        <v>522371.0444804651</v>
       </c>
       <c r="N4" t="n">
-        <v>520523.330873152</v>
+        <v>520403.9137693999</v>
       </c>
       <c r="O4" t="n">
-        <v>447790.3844155956</v>
+        <v>447670.9673118435</v>
       </c>
       <c r="P4" t="n">
-        <v>446122.6297523503</v>
+        <v>446003.2126485982</v>
       </c>
     </row>
     <row r="5">
@@ -26449,25 +26449,25 @@
         <v>74642.611</v>
       </c>
       <c r="J5" t="n">
-        <v>74642.61100000245</v>
+        <v>74642.61100000089</v>
       </c>
       <c r="K5" t="n">
-        <v>74642.61100000245</v>
+        <v>74642.61100000089</v>
       </c>
       <c r="L5" t="n">
-        <v>74642.61100000245</v>
+        <v>74642.61100000089</v>
       </c>
       <c r="M5" t="n">
-        <v>64115.19300000244</v>
+        <v>64115.19300000089</v>
       </c>
       <c r="N5" t="n">
-        <v>64115.19300000244</v>
+        <v>64115.19300000089</v>
       </c>
       <c r="O5" t="n">
-        <v>55372.01700000244</v>
+        <v>55372.01700000089</v>
       </c>
       <c r="P5" t="n">
-        <v>55372.01700000244</v>
+        <v>55372.01700000089</v>
       </c>
     </row>
     <row r="6">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>241331.7600892166</v>
+        <v>241531.0747444312</v>
       </c>
       <c r="C6" t="n">
-        <v>474438.6822767049</v>
+        <v>474637.9969319199</v>
       </c>
       <c r="D6" t="n">
-        <v>476450.3296925289</v>
+        <v>476649.6443477441</v>
       </c>
       <c r="E6" t="n">
-        <v>-62265.3275063062</v>
+        <v>-62071.16908057357</v>
       </c>
       <c r="F6" t="n">
-        <v>551890.3379935306</v>
+        <v>552084.4964192623</v>
       </c>
       <c r="G6" t="n">
-        <v>553561.3061891505</v>
+        <v>553755.4646148841</v>
       </c>
       <c r="H6" t="n">
-        <v>555234.5935932748</v>
+        <v>555428.7520190063</v>
       </c>
       <c r="I6" t="n">
-        <v>556910.2169337763</v>
+        <v>557104.3753595066</v>
       </c>
       <c r="J6" t="n">
-        <v>171740.1931577433</v>
+        <v>171934.3515834815</v>
       </c>
       <c r="K6" t="n">
-        <v>560268.5394357252</v>
+        <v>560462.6978614571</v>
       </c>
       <c r="L6" t="n">
-        <v>561951.2731659031</v>
+        <v>562145.4315916332</v>
       </c>
       <c r="M6" t="n">
-        <v>484197.2031034984</v>
+        <v>484316.6202072448</v>
       </c>
       <c r="N6" t="n">
-        <v>548564.3338145629</v>
+        <v>548683.7509183099</v>
       </c>
       <c r="O6" t="n">
-        <v>340665.189114687</v>
+        <v>340784.606218433</v>
       </c>
       <c r="P6" t="n">
-        <v>514332.9437779314</v>
+        <v>514452.3608816781</v>
       </c>
     </row>
   </sheetData>
@@ -26883,25 +26883,25 @@
         <v>655</v>
       </c>
       <c r="J4" t="n">
-        <v>655.0000000000401</v>
+        <v>655.0000000000147</v>
       </c>
       <c r="K4" t="n">
-        <v>655.0000000000401</v>
+        <v>655.0000000000147</v>
       </c>
       <c r="L4" t="n">
-        <v>655.0000000000401</v>
+        <v>655.0000000000147</v>
       </c>
       <c r="M4" t="n">
-        <v>374.0000000000401</v>
+        <v>374.0000000000147</v>
       </c>
       <c r="N4" t="n">
-        <v>374.0000000000401</v>
+        <v>374.0000000000147</v>
       </c>
       <c r="O4" t="n">
-        <v>374.0000000000401</v>
+        <v>374.0000000000147</v>
       </c>
       <c r="P4" t="n">
-        <v>374.0000000000401</v>
+        <v>374.0000000000147</v>
       </c>
     </row>
   </sheetData>
@@ -26978,16 +26978,16 @@
         <v>-0</v>
       </c>
       <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>319</v>
+      </c>
+      <c r="F2" t="n">
         <v>-0</v>
       </c>
-      <c r="E2" t="n">
-        <v>319</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
@@ -26999,16 +26999,16 @@
         <v>319</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M2" t="n">
         <v>78</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>215</v>
@@ -27100,7 +27100,7 @@
         <v>-0</v>
       </c>
       <c r="J4" t="n">
-        <v>374.0000000000329</v>
+        <v>374.0000000000074</v>
       </c>
       <c r="K4" t="n">
         <v>-0</v>
@@ -27512,19 +27512,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
-        <v>268.5547338014611</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>325.5201396486123</v>
@@ -27533,7 +27533,7 @@
         <v>330.0491815260438</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>209.5726123064429</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27569,10 +27569,10 @@
         <v>400</v>
       </c>
       <c r="U3" t="n">
+        <v>46.70121580080843</v>
+      </c>
+      <c r="V3" t="n">
         <v>400</v>
-      </c>
-      <c r="V3" t="n">
-        <v>40.51066719152016</v>
       </c>
       <c r="W3" t="n">
         <v>400</v>
@@ -27591,10 +27591,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C4" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D4" t="n">
         <v>285.5362180555555</v>
@@ -27606,22 +27606,22 @@
         <v>274.3828559677419</v>
       </c>
       <c r="G4" t="n">
-        <v>399.3804500438035</v>
+        <v>400</v>
       </c>
       <c r="H4" t="n">
         <v>227.1357818393235</v>
       </c>
       <c r="I4" t="n">
-        <v>171.1020457840527</v>
+        <v>400</v>
       </c>
       <c r="J4" t="n">
-        <v>22.26478490148153</v>
+        <v>60.51040441097491</v>
       </c>
       <c r="K4" t="n">
         <v>400</v>
       </c>
       <c r="L4" t="n">
-        <v>400</v>
+        <v>396.2015953708939</v>
       </c>
       <c r="M4" t="n">
         <v>400</v>
@@ -27645,13 +27645,13 @@
         <v>359.1680042930194</v>
       </c>
       <c r="T4" t="n">
-        <v>400</v>
+        <v>209.2386648669134</v>
       </c>
       <c r="U4" t="n">
         <v>400</v>
       </c>
       <c r="V4" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
         <v>400</v>
@@ -27660,7 +27660,7 @@
         <v>400</v>
       </c>
       <c r="Y4" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="5">
@@ -27688,10 +27688,10 @@
         <v>400</v>
       </c>
       <c r="H5" t="n">
-        <v>400</v>
+        <v>398.2013121321735</v>
       </c>
       <c r="I5" t="n">
-        <v>132.4740095033003</v>
+        <v>134.2726973711268</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27755,10 +27755,10 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>224.1210639876019</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
         <v>339.6362423378769</v>
@@ -27767,7 +27767,7 @@
         <v>325.5201396486123</v>
       </c>
       <c r="H6" t="n">
-        <v>201.0782250907744</v>
+        <v>330.0491815260438</v>
       </c>
       <c r="I6" t="n">
         <v>209.5726123064429</v>
@@ -27812,10 +27812,10 @@
         <v>400</v>
       </c>
       <c r="W6" t="n">
-        <v>400</v>
+        <v>58.37314290982852</v>
       </c>
       <c r="X6" t="n">
-        <v>400</v>
+        <v>45.86273944538755</v>
       </c>
       <c r="Y6" t="n">
         <v>399.3913927661343</v>
@@ -27846,16 +27846,16 @@
         <v>244.8599384153005</v>
       </c>
       <c r="H7" t="n">
+        <v>377.4742252104027</v>
+      </c>
+      <c r="I7" t="n">
         <v>400</v>
-      </c>
-      <c r="I7" t="n">
-        <v>171.1020457840527</v>
       </c>
       <c r="J7" t="n">
         <v>396.2647849014816</v>
       </c>
       <c r="K7" t="n">
-        <v>267.1509377355693</v>
+        <v>400</v>
       </c>
       <c r="L7" t="n">
         <v>400</v>
@@ -27888,10 +27888,10 @@
         <v>400</v>
       </c>
       <c r="V7" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
-        <v>364.7643617457065</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
         <v>247.4436454301076</v>
@@ -27925,10 +27925,10 @@
         <v>400</v>
       </c>
       <c r="H8" t="n">
-        <v>400</v>
+        <v>398.2013121321734</v>
       </c>
       <c r="I8" t="n">
-        <v>132.4740095033003</v>
+        <v>134.2726973711268</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27995,7 +27995,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>35.20223401754447</v>
       </c>
       <c r="F9" t="n">
         <v>339.6362423378769</v>
@@ -28004,7 +28004,7 @@
         <v>325.5201396486123</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>330.0491815260438</v>
       </c>
       <c r="I9" t="n">
         <v>209.5726123064429</v>
@@ -28034,13 +28034,13 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>375.4798020188998</v>
+        <v>400</v>
       </c>
       <c r="S9" t="n">
-        <v>88.48881128536601</v>
+        <v>400</v>
       </c>
       <c r="T9" t="n">
-        <v>30.47344446279683</v>
+        <v>400</v>
       </c>
       <c r="U9" t="n">
         <v>400</v>
@@ -28052,10 +28052,10 @@
         <v>400</v>
       </c>
       <c r="X9" t="n">
-        <v>400</v>
+        <v>45.86273944538755</v>
       </c>
       <c r="Y9" t="n">
-        <v>399.3913927661343</v>
+        <v>25.39139276613435</v>
       </c>
     </row>
     <row r="10">
@@ -28065,10 +28065,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C10" t="n">
-        <v>378.2488824783463</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D10" t="n">
         <v>285.5362180555555</v>
@@ -28077,25 +28077,25 @@
         <v>400</v>
       </c>
       <c r="F10" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G10" t="n">
-        <v>400</v>
+        <v>250.2081295226739</v>
       </c>
       <c r="H10" t="n">
         <v>227.1357818393235</v>
       </c>
       <c r="I10" t="n">
-        <v>400</v>
+        <v>171.1020457840527</v>
       </c>
       <c r="J10" t="n">
-        <v>396.2647849014816</v>
+        <v>22.26478490148153</v>
       </c>
       <c r="K10" t="n">
         <v>267.1509377355693</v>
       </c>
       <c r="L10" t="n">
-        <v>400</v>
+        <v>396.2015953708939</v>
       </c>
       <c r="M10" t="n">
         <v>400</v>
@@ -28122,13 +28122,13 @@
         <v>400</v>
       </c>
       <c r="U10" t="n">
-        <v>150.9483584875727</v>
+        <v>400</v>
       </c>
       <c r="V10" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W10" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X10" t="n">
         <v>400</v>
@@ -28232,10 +28232,10 @@
         <v>319</v>
       </c>
       <c r="E12" t="n">
-        <v>319</v>
+        <v>286.0053395461674</v>
       </c>
       <c r="F12" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -28244,7 +28244,7 @@
         <v>319</v>
       </c>
       <c r="I12" t="n">
-        <v>189.9476123064429</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -28271,7 +28271,7 @@
         <v>72.31352924142297</v>
       </c>
       <c r="R12" t="n">
-        <v>96.05772723972416</v>
+        <v>319</v>
       </c>
       <c r="S12" t="n">
         <v>319</v>
@@ -28280,7 +28280,7 @@
         <v>319</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="V12" t="n">
         <v>319</v>
@@ -28289,10 +28289,10 @@
         <v>319</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="Y12" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -28466,16 +28466,16 @@
         <v>319</v>
       </c>
       <c r="D15" t="n">
-        <v>96.05772723972416</v>
+        <v>319</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="H15" t="n">
         <v>319</v>
@@ -28520,13 +28520,13 @@
         <v>319</v>
       </c>
       <c r="V15" t="n">
-        <v>319</v>
+        <v>96.05772723972427</v>
       </c>
       <c r="W15" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
         <v>319</v>
@@ -28545,7 +28545,7 @@
         <v>319</v>
       </c>
       <c r="D16" t="n">
-        <v>319</v>
+        <v>319.0000000000023</v>
       </c>
       <c r="E16" t="n">
         <v>319</v>
@@ -28697,16 +28697,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>96.0577272397245</v>
+        <v>319</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="F18" t="n">
         <v>319</v>
@@ -28757,16 +28757,16 @@
         <v>319</v>
       </c>
       <c r="V18" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>319</v>
+        <v>96.05772723972444</v>
       </c>
     </row>
     <row r="19">
@@ -28782,7 +28782,7 @@
         <v>319</v>
       </c>
       <c r="D19" t="n">
-        <v>319</v>
+        <v>319.0000000000024</v>
       </c>
       <c r="E19" t="n">
         <v>319</v>
@@ -28934,19 +28934,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>96.0577272397245</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>96.0577272397245</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="F21" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>319</v>
@@ -29082,7 +29082,7 @@
         <v>319</v>
       </c>
       <c r="Y22" t="n">
-        <v>319</v>
+        <v>319.0000000000018</v>
       </c>
     </row>
     <row r="23">
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>158.2009556122953</v>
+        <v>158.200955612214</v>
       </c>
       <c r="S23" t="n">
         <v>319</v>
@@ -29177,16 +29177,16 @@
         <v>319</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>168.3712564811474</v>
       </c>
       <c r="G24" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>319</v>
@@ -29216,19 +29216,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>72.31352924142297</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>96.05772723972422</v>
+        <v>319</v>
       </c>
       <c r="T24" t="n">
         <v>319</v>
       </c>
       <c r="U24" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
         <v>319</v>
@@ -29420,16 +29420,16 @@
         <v>319</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="G27" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>319</v>
       </c>
       <c r="I27" t="n">
-        <v>189.9476123064429</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -29459,7 +29459,7 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="T27" t="n">
         <v>319</v>
@@ -29468,7 +29468,7 @@
         <v>319</v>
       </c>
       <c r="V27" t="n">
-        <v>168.3712564811476</v>
+        <v>39.31886878759065</v>
       </c>
       <c r="W27" t="n">
         <v>319</v>
@@ -29651,13 +29651,13 @@
         <v>319</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>96.05772723972461</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>319</v>
@@ -29699,7 +29699,7 @@
         <v>319</v>
       </c>
       <c r="T30" t="n">
-        <v>96.0577272397241</v>
+        <v>319</v>
       </c>
       <c r="U30" t="n">
         <v>319</v>
@@ -29882,7 +29882,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="C33" t="n">
         <v>319</v>
@@ -29894,16 +29894,16 @@
         <v>319</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="G33" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>286.0053395461674</v>
+        <v>168.3712564811478</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>189.9476123064429</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -29927,7 +29927,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>72.31352924142297</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>319</v>
@@ -29942,13 +29942,13 @@
         <v>319</v>
       </c>
       <c r="V33" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="Y33" t="n">
         <v>319</v>
@@ -29985,7 +29985,7 @@
         <v>319</v>
       </c>
       <c r="J34" t="n">
-        <v>319.000000000013</v>
+        <v>319</v>
       </c>
       <c r="K34" t="n">
         <v>319</v>
@@ -30119,7 +30119,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>384.5565566463266</v>
+        <v>10.55655664630652</v>
       </c>
       <c r="C36" t="n">
         <v>361.0999124455193</v>
@@ -30128,7 +30128,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
         <v>339.6362423378769</v>
@@ -30140,7 +30140,7 @@
         <v>324.5441815260438</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>189.9476123064429</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -30164,31 +30164,31 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>72.31352924142297</v>
       </c>
       <c r="R36" t="n">
         <v>397</v>
       </c>
       <c r="S36" t="n">
-        <v>397</v>
+        <v>287.5297981762669</v>
       </c>
       <c r="T36" t="n">
-        <v>397</v>
+        <v>28.17594446277674</v>
       </c>
       <c r="U36" t="n">
         <v>397</v>
       </c>
       <c r="V36" t="n">
-        <v>397</v>
+        <v>40.51066719150012</v>
       </c>
       <c r="W36" t="n">
         <v>397</v>
       </c>
       <c r="X36" t="n">
-        <v>164.7582558341274</v>
+        <v>397</v>
       </c>
       <c r="Y36" t="n">
-        <v>25.39139276607611</v>
+        <v>397</v>
       </c>
     </row>
     <row r="37">
@@ -30210,7 +30210,7 @@
         <v>280.9809048369565</v>
       </c>
       <c r="F37" t="n">
-        <v>274.3828559677419</v>
+        <v>397</v>
       </c>
       <c r="G37" t="n">
         <v>244.3820695628415</v>
@@ -30225,10 +30225,10 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>211.6312656044217</v>
+        <v>397</v>
       </c>
       <c r="L37" t="n">
-        <v>325.1555297971234</v>
+        <v>397</v>
       </c>
       <c r="M37" t="n">
         <v>397</v>
@@ -30249,25 +30249,25 @@
         <v>397</v>
       </c>
       <c r="S37" t="n">
-        <v>397</v>
+        <v>350.8400534733473</v>
       </c>
       <c r="T37" t="n">
         <v>397</v>
       </c>
       <c r="U37" t="n">
-        <v>232.3958458768651</v>
+        <v>150.9222929138022</v>
       </c>
       <c r="V37" t="n">
         <v>397</v>
       </c>
       <c r="W37" t="n">
-        <v>397</v>
+        <v>254.3377980095405</v>
       </c>
       <c r="X37" t="n">
         <v>247.4436454301076</v>
       </c>
       <c r="Y37" t="n">
-        <v>397</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="38">
@@ -30362,7 +30362,7 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
         <v>342.6720972219126</v>
@@ -30371,10 +30371,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G39" t="n">
-        <v>324.9501396486123</v>
+        <v>71.79592809029421</v>
       </c>
       <c r="H39" t="n">
-        <v>324.5441815260438</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -30404,13 +30404,13 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>137.0420953662576</v>
+        <v>397</v>
       </c>
       <c r="S39" t="n">
         <v>397</v>
       </c>
       <c r="T39" t="n">
-        <v>397</v>
+        <v>28.17594446275127</v>
       </c>
       <c r="U39" t="n">
         <v>397</v>
@@ -30419,7 +30419,7 @@
         <v>397</v>
       </c>
       <c r="W39" t="n">
-        <v>58.37314290973572</v>
+        <v>397</v>
       </c>
       <c r="X39" t="n">
         <v>397</v>
@@ -30444,19 +30444,19 @@
         <v>285.5362180555555</v>
       </c>
       <c r="E40" t="n">
-        <v>397</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F40" t="n">
-        <v>310.1143408917476</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G40" t="n">
-        <v>397</v>
+        <v>244.3820695628415</v>
       </c>
       <c r="H40" t="n">
         <v>222.8870933147334</v>
       </c>
       <c r="I40" t="n">
-        <v>156.7312261119215</v>
+        <v>397</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -30495,16 +30495,16 @@
         <v>150.9222929138022</v>
       </c>
       <c r="V40" t="n">
+        <v>199.1703102162162</v>
+      </c>
+      <c r="W40" t="n">
         <v>397</v>
       </c>
-      <c r="W40" t="n">
-        <v>226.3728098387097</v>
-      </c>
       <c r="X40" t="n">
-        <v>247.4436454301076</v>
+        <v>397</v>
       </c>
       <c r="Y40" t="n">
-        <v>397</v>
+        <v>338.7458816887303</v>
       </c>
     </row>
     <row r="41">
@@ -30611,7 +30611,7 @@
         <v>293</v>
       </c>
       <c r="H42" t="n">
-        <v>293</v>
+        <v>290.613226554518</v>
       </c>
       <c r="I42" t="n">
         <v>189.9476123064429</v>
@@ -30656,7 +30656,7 @@
         <v>293</v>
       </c>
       <c r="W42" t="n">
-        <v>290.6132265544192</v>
+        <v>293</v>
       </c>
       <c r="X42" t="n">
         <v>293</v>
@@ -30848,7 +30848,7 @@
         <v>293</v>
       </c>
       <c r="H45" t="n">
-        <v>293</v>
+        <v>290.6132265545179</v>
       </c>
       <c r="I45" t="n">
         <v>189.9476123064429</v>
@@ -30875,7 +30875,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>69.92675579584207</v>
+        <v>72.31352924142297</v>
       </c>
       <c r="R45" t="n">
         <v>293</v>
@@ -34743,28 +34743,28 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>373.9999999999999</v>
+        <v>52.1599296482412</v>
       </c>
       <c r="L2" t="n">
-        <v>64.70900502512563</v>
+        <v>64.70900502512562</v>
       </c>
       <c r="M2" t="n">
         <v>374</v>
       </c>
       <c r="N2" t="n">
-        <v>235.5012052109774</v>
+        <v>183.3412755627362</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="P2" t="n">
         <v>58.67867865278593</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34877,10 +34877,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -34892,22 +34892,22 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>154.5205116285029</v>
+        <v>155.1400615846995</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>228.8979542159473</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>38.24561950949337</v>
       </c>
       <c r="K4" t="n">
         <v>132.8490622644307</v>
       </c>
       <c r="L4" t="n">
-        <v>3.798404629106074</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -34931,13 +34931,13 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>190.7613351330866</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
         <v>249.0516415124273</v>
       </c>
       <c r="V4" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>173.6271901612903</v>
@@ -34946,7 +34946,7 @@
         <v>152.5563545698924</v>
       </c>
       <c r="Y4" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -34983,19 +34983,19 @@
         <v>374</v>
       </c>
       <c r="K5" t="n">
-        <v>373.9999999999999</v>
+        <v>52.15992964824119</v>
       </c>
       <c r="L5" t="n">
-        <v>300.2102102361032</v>
+        <v>64.70900502512563</v>
       </c>
       <c r="M5" t="n">
         <v>374</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>183.3412755627363</v>
       </c>
       <c r="P5" t="n">
         <v>58.67867865278593</v>
@@ -35132,16 +35132,16 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>172.8642181606765</v>
+        <v>150.3384433710791</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>228.8979542159473</v>
       </c>
       <c r="J7" t="n">
         <v>374</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>132.8490622644307</v>
       </c>
       <c r="L7" t="n">
         <v>3.798404629106074</v>
@@ -35174,10 +35174,10 @@
         <v>249.0516415124273</v>
       </c>
       <c r="V7" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>138.3915519069968</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -35217,19 +35217,19 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>52.1599296482412</v>
+      </c>
+      <c r="L8" t="n">
+        <v>64.70900502512562</v>
+      </c>
+      <c r="M8" t="n">
         <v>374</v>
       </c>
-      <c r="K8" t="n">
-        <v>52.15992964824119</v>
-      </c>
-      <c r="L8" t="n">
-        <v>64.70900502512563</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
       <c r="N8" t="n">
-        <v>242.0199542155221</v>
+        <v>374</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -35238,7 +35238,7 @@
         <v>374</v>
       </c>
       <c r="Q8" t="n">
-        <v>374</v>
+        <v>242.0199542155222</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35351,10 +35351,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C10" t="n">
-        <v>105.5236358303016</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -35363,25 +35363,25 @@
         <v>119.0190951630435</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
-        <v>155.1400615846995</v>
+        <v>5.348191107373398</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>228.8979542159473</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3.798404629106074</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -35402,19 +35402,19 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>40.83199570698065</v>
+        <v>40.83199570698063</v>
       </c>
       <c r="T10" t="n">
         <v>190.7613351330866</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>249.0516415124273</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X10" t="n">
         <v>152.5563545698924</v>
@@ -35463,10 +35463,10 @@
         <v>232.8255376884422</v>
       </c>
       <c r="M11" t="n">
-        <v>655</v>
+        <v>607.3433266784072</v>
       </c>
       <c r="N11" t="n">
-        <v>4.989832208681229</v>
+        <v>655.0000000000006</v>
       </c>
       <c r="O11" t="n">
         <v>178.3365374610834</v>
@@ -35475,7 +35475,7 @@
         <v>211.8739801603236</v>
       </c>
       <c r="Q11" t="n">
-        <v>602.3534944697265</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35615,7 +35615,7 @@
         <v>330.5205429673709</v>
       </c>
       <c r="K13" t="n">
-        <v>107.3687343955782</v>
+        <v>107.3687343955783</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -35691,28 +35691,28 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>90.1777625991308</v>
+        <v>520.4824991852875</v>
       </c>
       <c r="K14" t="n">
-        <v>187.673472361809</v>
+        <v>187.6734723618091</v>
       </c>
       <c r="L14" t="n">
-        <v>232.8255376884423</v>
+        <v>232.8255376884422</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>607.3433266784072</v>
       </c>
       <c r="N14" t="n">
-        <v>655</v>
+        <v>655.0000000000006</v>
       </c>
       <c r="O14" t="n">
-        <v>613.6311062559213</v>
+        <v>178.3365374610834</v>
       </c>
       <c r="P14" t="n">
         <v>211.8739801603236</v>
       </c>
       <c r="Q14" t="n">
-        <v>602.3534944697265</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35831,7 +35831,7 @@
         <v>46.27475335195533</v>
       </c>
       <c r="D16" t="n">
-        <v>33.46378194444452</v>
+        <v>33.46378194444684</v>
       </c>
       <c r="E16" t="n">
         <v>38.01909516304346</v>
@@ -35852,7 +35852,7 @@
         <v>330.5205429673709</v>
       </c>
       <c r="K16" t="n">
-        <v>107.3687343955782</v>
+        <v>107.3687343955783</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -35937,19 +35937,19 @@
         <v>232.8255376884422</v>
       </c>
       <c r="M17" t="n">
-        <v>4.989832208681229</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>655</v>
+        <v>655.0000000000006</v>
       </c>
       <c r="O17" t="n">
-        <v>178.3365374610834</v>
+        <v>655.0000000000006</v>
       </c>
       <c r="P17" t="n">
         <v>211.8739801603236</v>
       </c>
       <c r="Q17" t="n">
-        <v>602.3534944697265</v>
+        <v>130.6798641394899</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36068,7 +36068,7 @@
         <v>46.27475335195533</v>
       </c>
       <c r="D19" t="n">
-        <v>33.46378194444452</v>
+        <v>33.46378194444695</v>
       </c>
       <c r="E19" t="n">
         <v>38.01909516304346</v>
@@ -36165,19 +36165,19 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>90.1777625991308</v>
+        <v>520.4824991852875</v>
       </c>
       <c r="K20" t="n">
-        <v>187.673472361809</v>
+        <v>187.6734723618091</v>
       </c>
       <c r="L20" t="n">
-        <v>615.4736009530067</v>
+        <v>232.8255376884422</v>
       </c>
       <c r="M20" t="n">
-        <v>655</v>
+        <v>4.98983220868077</v>
       </c>
       <c r="N20" t="n">
-        <v>655</v>
+        <v>655.0000000000006</v>
       </c>
       <c r="O20" t="n">
         <v>178.3365374610834</v>
@@ -36186,7 +36186,7 @@
         <v>211.8739801603236</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>602.3534944697265</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36368,7 +36368,7 @@
         <v>71.55635456989245</v>
       </c>
       <c r="Y22" t="n">
-        <v>31.53464715053764</v>
+        <v>31.53464715053941</v>
       </c>
     </row>
     <row r="23">
@@ -36402,19 +36402,19 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>520.4824991852875</v>
+        <v>90.1777625991308</v>
       </c>
       <c r="K23" t="n">
-        <v>654.9999999999999</v>
+        <v>622.9680411566466</v>
       </c>
       <c r="L23" t="n">
-        <v>372.8423367286591</v>
+        <v>232.8255376884423</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>655.0000000000006</v>
       </c>
       <c r="N23" t="n">
-        <v>655</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>178.3365374610834</v>
@@ -36423,10 +36423,10 @@
         <v>211.8739801603236</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>602.3534944697265</v>
       </c>
       <c r="R23" t="n">
-        <v>8.130331424939813e-11</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -36645,13 +36645,13 @@
         <v>187.6734723618091</v>
       </c>
       <c r="L26" t="n">
-        <v>232.8255376884422</v>
+        <v>655.0000000000148</v>
       </c>
       <c r="M26" t="n">
-        <v>655.0000000000128</v>
+        <v>237.8153698971667</v>
       </c>
       <c r="N26" t="n">
-        <v>4.989832208827529</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>178.3365374610834</v>
@@ -36876,7 +36876,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>90.1777625991308</v>
+        <v>520.4824991852875</v>
       </c>
       <c r="K29" t="n">
         <v>187.6734723618091</v>
@@ -36885,19 +36885,19 @@
         <v>232.8255376884422</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>655.0000000000028</v>
       </c>
       <c r="N29" t="n">
-        <v>655.0000000000203</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>655.0000000000203</v>
+        <v>655.0000000000028</v>
       </c>
       <c r="P29" t="n">
-        <v>655.0000000000203</v>
+        <v>211.8739801603236</v>
       </c>
       <c r="Q29" t="n">
-        <v>117.8585808859909</v>
+        <v>130.6798641395028</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37037,7 +37037,7 @@
         <v>330.5205429673709</v>
       </c>
       <c r="K31" t="n">
-        <v>107.3687343955782</v>
+        <v>107.3687343955783</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -37122,10 +37122,10 @@
         <v>232.8255376884422</v>
       </c>
       <c r="M32" t="n">
-        <v>655.0000000000329</v>
+        <v>655.0000000000038</v>
       </c>
       <c r="N32" t="n">
-        <v>607.3433266785337</v>
+        <v>607.3433266784621</v>
       </c>
       <c r="O32" t="n">
         <v>178.3365374610834</v>
@@ -37271,10 +37271,10 @@
         <v>162.2687738880785</v>
       </c>
       <c r="J34" t="n">
-        <v>330.5205429673839</v>
+        <v>330.5205429673709</v>
       </c>
       <c r="K34" t="n">
-        <v>107.3687343955782</v>
+        <v>107.3687343955783</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -37359,10 +37359,10 @@
         <v>232.8255376884422</v>
       </c>
       <c r="M35" t="n">
-        <v>206.0015986182004</v>
+        <v>206.0015986181378</v>
       </c>
       <c r="N35" t="n">
-        <v>374.0000000000583</v>
+        <v>374.0000000000201</v>
       </c>
       <c r="O35" t="n">
         <v>178.3365374610834</v>
@@ -37429,19 +37429,19 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>167.0143075451844</v>
+        <v>199.7892383131474</v>
       </c>
       <c r="K36" t="n">
         <v>318.5740338860743</v>
       </c>
       <c r="L36" t="n">
-        <v>57.40142568134173</v>
+        <v>364.561846908725</v>
       </c>
       <c r="M36" t="n">
         <v>286.9650421645043</v>
       </c>
       <c r="N36" t="n">
-        <v>339.9353519954473</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>46.59266649806909</v>
@@ -37496,7 +37496,7 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>122.6171440322581</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -37511,10 +37511,10 @@
         <v>11.52054296737091</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>185.3687343955783</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>71.84447020287656</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -37535,25 +37535,25 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>46.15994652665276</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
         <v>189.8031384117751</v>
       </c>
       <c r="U37" t="n">
-        <v>81.47355296306289</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
         <v>197.8296897837838</v>
       </c>
       <c r="W37" t="n">
-        <v>170.6271901612903</v>
+        <v>27.96498817083082</v>
       </c>
       <c r="X37" t="n">
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>109.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -37596,19 +37596,19 @@
         <v>232.8255376884422</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>43.87557877839053</v>
       </c>
       <c r="N38" t="n">
-        <v>43.87557877839674</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>178.3365374610834</v>
       </c>
       <c r="P38" t="n">
-        <v>374.0000000000928</v>
+        <v>374.0000000000455</v>
       </c>
       <c r="Q38" t="n">
-        <v>374.0000000000928</v>
+        <v>374.0000000000455</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37669,16 +37669,16 @@
         <v>199.7892383131474</v>
       </c>
       <c r="K39" t="n">
-        <v>318.5740338860743</v>
+        <v>22.69379302306083</v>
       </c>
       <c r="L39" t="n">
-        <v>57.40142568134173</v>
+        <v>374.0000000000455</v>
       </c>
       <c r="M39" t="n">
         <v>286.9650421645043</v>
       </c>
       <c r="N39" t="n">
-        <v>307.1604212274839</v>
+        <v>286.4420877716931</v>
       </c>
       <c r="O39" t="n">
         <v>46.59266649806909</v>
@@ -37730,19 +37730,19 @@
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>116.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>35.73148492400568</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>152.6179304371585</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>240.2687738880785</v>
       </c>
       <c r="J40" t="n">
         <v>11.52054296737091</v>
@@ -37781,16 +37781,16 @@
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>197.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>170.6271901612903</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>149.5563545698924</v>
       </c>
       <c r="Y40" t="n">
-        <v>109.5346471505376</v>
+        <v>51.28052883926787</v>
       </c>
     </row>
     <row r="41">
@@ -37827,7 +37827,7 @@
         <v>90.1777625991308</v>
       </c>
       <c r="K41" t="n">
-        <v>187.673472361809</v>
+        <v>374.0000000000147</v>
       </c>
       <c r="L41" t="n">
         <v>232.8255376884422</v>
@@ -37836,7 +37836,7 @@
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>374.0000000001383</v>
+        <v>19.67507097987944</v>
       </c>
       <c r="O41" t="n">
         <v>178.3365374610834</v>
@@ -37845,7 +37845,7 @@
         <v>211.8739801603236</v>
       </c>
       <c r="Q41" t="n">
-        <v>206.0015986181203</v>
+        <v>374.0000000000728</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37903,22 +37903,22 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>199.7892383131474</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>318.5740338860743</v>
+        <v>22.69379302306083</v>
       </c>
       <c r="L42" t="n">
-        <v>364.5618469088258</v>
+        <v>374.0000000000728</v>
       </c>
       <c r="M42" t="n">
         <v>286.9650421645043</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>339.9353519954473</v>
       </c>
       <c r="O42" t="n">
-        <v>46.59266649806909</v>
+        <v>192.8886405874349</v>
       </c>
       <c r="P42" t="n">
         <v>264.4060611184268</v>
@@ -38070,19 +38070,19 @@
         <v>232.8255376884422</v>
       </c>
       <c r="M44" t="n">
-        <v>374.0000000002656</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>206.0015986179931</v>
+        <v>43.87557877816133</v>
       </c>
       <c r="O44" t="n">
         <v>178.3365374610834</v>
       </c>
       <c r="P44" t="n">
-        <v>211.8739801603236</v>
+        <v>374.0000000001601</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>374.0000000001601</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38143,19 +38143,19 @@
         <v>199.7892383131474</v>
       </c>
       <c r="K45" t="n">
-        <v>318.5740338860743</v>
+        <v>22.69379302306083</v>
       </c>
       <c r="L45" t="n">
-        <v>57.40142568134173</v>
+        <v>374.0000000001601</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>286.9650421645043</v>
       </c>
       <c r="N45" t="n">
-        <v>339.9353519954473</v>
+        <v>286.4420877715784</v>
       </c>
       <c r="O45" t="n">
-        <v>300.78277789461</v>
+        <v>46.59266649806909</v>
       </c>
       <c r="P45" t="n">
         <v>264.4060611184268</v>
